--- a/research/traditional_assets/database/data/norway/norway_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ28"/>
+  <dimension ref="A1:AQ27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06605</v>
+        <v>0.0764</v>
       </c>
       <c r="E2">
-        <v>0.09245</v>
-      </c>
-      <c r="F2">
-        <v>0.1425</v>
+        <v>0.0824</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1274.49</v>
+        <v>1105.9</v>
       </c>
       <c r="L2">
-        <v>0.4298376081347701</v>
+        <v>0.4310627085347221</v>
       </c>
       <c r="M2">
-        <v>333.157004</v>
+        <v>781.17696</v>
       </c>
       <c r="N2">
-        <v>0.03085787097670542</v>
+        <v>0.08840623705611676</v>
       </c>
       <c r="O2">
-        <v>0.261404172649452</v>
+        <v>0.7063721493805949</v>
       </c>
       <c r="P2">
-        <v>317.189004</v>
+        <v>746.7709600000001</v>
       </c>
       <c r="Q2">
-        <v>0.02937887315333673</v>
+        <v>0.08451249063513586</v>
       </c>
       <c r="R2">
-        <v>0.2488752395075677</v>
+        <v>0.6752608373270639</v>
       </c>
       <c r="S2">
-        <v>15.968</v>
+        <v>34.40600000000001</v>
       </c>
       <c r="T2">
-        <v>0.04792935405314186</v>
+        <v>0.04404379770750024</v>
       </c>
       <c r="U2">
-        <v>1600.207</v>
+        <v>1012.96</v>
       </c>
       <c r="V2">
-        <v>0.1482153475663409</v>
+        <v>0.1146372543915837</v>
       </c>
       <c r="W2">
-        <v>0.09356686919410551</v>
+        <v>0.07427937915742794</v>
       </c>
       <c r="X2">
-        <v>0.1258022069449052</v>
+        <v>0.1193248153454883</v>
       </c>
       <c r="Y2">
-        <v>-0.03223533775079973</v>
+        <v>-0.04504543618806039</v>
       </c>
       <c r="Z2">
-        <v>0.06601803390789354</v>
+        <v>0.05228254690541396</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03960615607549684</v>
+        <v>0.05544028787048495</v>
       </c>
       <c r="AC2">
-        <v>-0.03960615607549684</v>
+        <v>-0.05544028787048495</v>
       </c>
       <c r="AD2">
-        <v>37677.167</v>
+        <v>33305.087</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>37677.167</v>
+        <v>33305.087</v>
       </c>
       <c r="AG2">
-        <v>36076.96</v>
+        <v>32292.127</v>
       </c>
       <c r="AH2">
-        <v>0.7772708221146133</v>
+        <v>0.7903192703539071</v>
       </c>
       <c r="AI2">
-        <v>0.7401726103086962</v>
+        <v>0.7483534637754615</v>
       </c>
       <c r="AJ2">
-        <v>0.7696670994631077</v>
+        <v>0.7851549929784438</v>
       </c>
       <c r="AK2">
-        <v>0.7317395023143617</v>
+        <v>0.7424923709852725</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Høland og Setskog Sparebank (OB:HSPG)</t>
+          <t>Sparebanken Møre (OB:MORG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.036</v>
+        <v>0.0467</v>
       </c>
       <c r="E3">
-        <v>0.018</v>
+        <v>0.0605</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>6.66</v>
+        <v>63.3</v>
       </c>
       <c r="L3">
-        <v>0.3741573033707865</v>
+        <v>0.4288617886178862</v>
       </c>
       <c r="M3">
-        <v>0.394224</v>
+        <v>57.2</v>
       </c>
       <c r="N3">
-        <v>0.03458105263157894</v>
+        <v>0.1353846153846154</v>
       </c>
       <c r="O3">
-        <v>0.05919279279279278</v>
+        <v>0.9036334913112165</v>
       </c>
       <c r="P3">
-        <v>0.394224</v>
+        <v>25.1</v>
       </c>
       <c r="Q3">
-        <v>0.03458105263157894</v>
+        <v>0.05940828402366864</v>
       </c>
       <c r="R3">
-        <v>0.05919279279279278</v>
+        <v>0.39652448657188</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.5611888111888111</v>
       </c>
       <c r="U3">
-        <v>22.3</v>
+        <v>62.3</v>
       </c>
       <c r="V3">
-        <v>1.956140350877193</v>
+        <v>0.1474556213017751</v>
       </c>
       <c r="W3">
-        <v>0.09073569482288828</v>
+        <v>0.07278371852362883</v>
       </c>
       <c r="X3">
-        <v>0.4572005280152834</v>
+        <v>0.1828108115698041</v>
       </c>
       <c r="Y3">
-        <v>-0.3664648331923951</v>
+        <v>-0.1100270930461753</v>
       </c>
       <c r="Z3">
-        <v>0.07343234323432343</v>
+        <v>0.0309641688344382</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03915803146613662</v>
+        <v>0.05437290700242188</v>
       </c>
       <c r="AC3">
-        <v>-0.03915803146613662</v>
+        <v>-0.05437290700242188</v>
       </c>
       <c r="AD3">
-        <v>227.5</v>
+        <v>3104.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>227.5</v>
+        <v>3104.6</v>
       </c>
       <c r="AG3">
-        <v>205.2</v>
+        <v>3042.3</v>
       </c>
       <c r="AH3">
-        <v>0.9522812892423608</v>
+        <v>0.8802132063168042</v>
       </c>
       <c r="AI3">
-        <v>0.7238307349665924</v>
+        <v>0.8109604785413891</v>
       </c>
       <c r="AJ3">
-        <v>0.9473684210526315</v>
+        <v>0.878059339644424</v>
       </c>
       <c r="AK3">
-        <v>0.7027397260273972</v>
+        <v>0.8078332448220923</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sogn Sparebank (OB:SOGN)</t>
+          <t>Skue Sparebank (OB:SKUE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="E4">
-        <v>0.194</v>
+        <v>0.166</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>5.33</v>
+        <v>15.3</v>
       </c>
       <c r="L4">
-        <v>0.2928571428571429</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="M4">
-        <v>0.664</v>
+        <v>2.126</v>
       </c>
       <c r="N4">
-        <v>0.06574257425742575</v>
+        <v>0.04392561983471074</v>
       </c>
       <c r="O4">
-        <v>0.124577861163227</v>
+        <v>0.1389542483660131</v>
       </c>
       <c r="P4">
-        <v>0.664</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>0.06574257425742575</v>
+        <v>0.04380165289256199</v>
       </c>
       <c r="R4">
-        <v>0.124577861163227</v>
+        <v>0.138562091503268</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.005999999999999783</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.00282220131702718</v>
       </c>
       <c r="U4">
-        <v>81</v>
+        <v>8.73</v>
       </c>
       <c r="V4">
-        <v>8.01980198019802</v>
+        <v>0.1803719008264463</v>
       </c>
       <c r="W4">
-        <v>0.05444330949948927</v>
+        <v>0.0759682224428997</v>
       </c>
       <c r="X4">
-        <v>0.2357295072707972</v>
+        <v>0.1819657076326278</v>
       </c>
       <c r="Y4">
-        <v>-0.1812861977713079</v>
+        <v>-0.1059974851897281</v>
       </c>
       <c r="Z4">
-        <v>0.1571675302245251</v>
+        <v>0.06260604004071937</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03929391557666059</v>
+        <v>0.05437774165692029</v>
       </c>
       <c r="AC4">
-        <v>-0.03929391557666059</v>
+        <v>-0.05437774165692029</v>
       </c>
       <c r="AD4">
-        <v>94.09999999999999</v>
+        <v>353.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>94.09999999999999</v>
+        <v>353.2</v>
       </c>
       <c r="AG4">
-        <v>13.09999999999999</v>
+        <v>344.47</v>
       </c>
       <c r="AH4">
-        <v>0.9030710172744723</v>
+        <v>0.8794820717131474</v>
       </c>
       <c r="AI4">
-        <v>0.4592484138604198</v>
+        <v>0.6609281437125749</v>
       </c>
       <c r="AJ4">
-        <v>0.5646551724137929</v>
+        <v>0.876804031868048</v>
       </c>
       <c r="AK4">
-        <v>0.105730427764326</v>
+        <v>0.6552970494797116</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Skue Sparebank (OB:SKUE)</t>
+          <t>Sandnes Sparebank (OB:SADG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0852</v>
+        <v>0.0416</v>
       </c>
       <c r="E5">
-        <v>0.0483</v>
+        <v>0.094</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,85 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>13.7</v>
+        <v>26.8</v>
       </c>
       <c r="L5">
-        <v>0.3577023498694517</v>
+        <v>0.4527027027027027</v>
       </c>
       <c r="M5">
-        <v>5.449999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="N5">
-        <v>0.1092184368737475</v>
+        <v>0.1093828399397893</v>
       </c>
       <c r="O5">
-        <v>0.3978102189781021</v>
+        <v>0.8134328358208955</v>
       </c>
       <c r="P5">
-        <v>1.44</v>
+        <v>21.8</v>
       </c>
       <c r="Q5">
-        <v>0.02885771543086172</v>
+        <v>0.1093828399397893</v>
       </c>
       <c r="R5">
-        <v>0.1051094890510949</v>
+        <v>0.8134328358208955</v>
       </c>
       <c r="S5">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.7357798165137616</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>10.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="V5">
-        <v>0.2084168336673347</v>
+        <v>0.3316608128449573</v>
       </c>
       <c r="W5">
-        <v>0.08096926713947991</v>
+        <v>0.07427937915742794</v>
       </c>
       <c r="X5">
-        <v>0.2079842181879624</v>
+        <v>0.1788765233656481</v>
       </c>
       <c r="Y5">
-        <v>-0.1270149510484825</v>
+        <v>-0.1045971442082202</v>
       </c>
       <c r="Z5">
-        <v>0.08069953645174884</v>
+        <v>0.03197407507426411</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03933362413574111</v>
+        <v>0.05439592782457549</v>
       </c>
       <c r="AC5">
-        <v>-0.03933362413574111</v>
+        <v>-0.05439592782457549</v>
       </c>
       <c r="AD5">
-        <v>398.4</v>
+        <v>1417.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>398.4</v>
+        <v>1417.5</v>
       </c>
       <c r="AG5">
-        <v>388</v>
+        <v>1351.4</v>
       </c>
       <c r="AH5">
-        <v>0.8886906089672095</v>
+        <v>0.8767318159327067</v>
       </c>
       <c r="AI5">
-        <v>0.6642214071357119</v>
+        <v>0.8249912699336515</v>
       </c>
       <c r="AJ5">
-        <v>0.8860470427038137</v>
+        <v>0.8714773973044432</v>
       </c>
       <c r="AK5">
-        <v>0.6582965727858839</v>
+        <v>0.8179892258337873</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sparebanken Møre (OB:MORG)</t>
+          <t>Nidaros Sparebank (OB:NISB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0167</v>
+        <v>0.0385</v>
       </c>
       <c r="E6">
-        <v>0.0155</v>
+        <v>0.0194</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>72.90000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="L6">
-        <v>0.4352238805970149</v>
+        <v>0.2341176470588235</v>
       </c>
       <c r="M6">
-        <v>7.68</v>
+        <v>0.6102</v>
       </c>
       <c r="N6">
-        <v>0.01544650040225262</v>
+        <v>0.04842857142857142</v>
       </c>
       <c r="O6">
-        <v>0.1053497942386831</v>
+        <v>0.3066331658291457</v>
       </c>
       <c r="P6">
-        <v>7.68</v>
+        <v>0.6102</v>
       </c>
       <c r="Q6">
-        <v>0.01544650040225262</v>
+        <v>0.04842857142857142</v>
       </c>
       <c r="R6">
-        <v>0.1053497942386831</v>
+        <v>0.3066331658291457</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>55</v>
+        <v>5.75</v>
       </c>
       <c r="V6">
-        <v>0.1106194690265487</v>
+        <v>0.4563492063492063</v>
       </c>
       <c r="W6">
-        <v>0.09635210150674069</v>
+        <v>0.03251633986928104</v>
       </c>
       <c r="X6">
-        <v>0.2072503365961335</v>
+        <v>0.1677305848271244</v>
       </c>
       <c r="Y6">
-        <v>-0.1108982350893929</v>
+        <v>-0.1352142449578434</v>
       </c>
       <c r="Z6">
-        <v>0.03997231767850324</v>
+        <v>0.05141823593106327</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03933483503118079</v>
+        <v>0.05446906363349432</v>
       </c>
       <c r="AC6">
-        <v>-0.03933483503118079</v>
+        <v>-0.05446906363349432</v>
       </c>
       <c r="AD6">
-        <v>3952.1</v>
+        <v>81.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3952.1</v>
+        <v>81.2</v>
       </c>
       <c r="AG6">
-        <v>3897.1</v>
+        <v>75.45</v>
       </c>
       <c r="AH6">
-        <v>0.8882520845975771</v>
+        <v>0.8656716417910448</v>
       </c>
       <c r="AI6">
-        <v>0.8196316728192791</v>
+        <v>0.6179604261796042</v>
       </c>
       <c r="AJ6">
-        <v>0.8868534237534988</v>
+        <v>0.8568994889267463</v>
       </c>
       <c r="AK6">
-        <v>0.8175505580263489</v>
+        <v>0.6004775169120573</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nidaros Sparebank (OB:NISB)</t>
+          <t>Sogn Sparebank (OB:SOGN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1200,6 +1197,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.127</v>
+      </c>
+      <c r="E7">
+        <v>0.212</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1213,28 +1216,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3.84</v>
+        <v>5.36</v>
       </c>
       <c r="L7">
-        <v>0.3310344827586207</v>
+        <v>0.3503267973856209</v>
       </c>
       <c r="M7">
-        <v>0.69495</v>
+        <v>0.506</v>
       </c>
       <c r="N7">
-        <v>0.04792758620689655</v>
+        <v>0.06009501187648456</v>
       </c>
       <c r="O7">
-        <v>0.1809765625</v>
+        <v>0.09440298507462686</v>
       </c>
       <c r="P7">
-        <v>0.69495</v>
+        <v>0.506</v>
       </c>
       <c r="Q7">
-        <v>0.04792758620689655</v>
+        <v>0.06009501187648456</v>
       </c>
       <c r="R7">
-        <v>0.1809765625</v>
+        <v>0.09440298507462686</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1243,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.489</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="V7">
-        <v>0.03372413793103448</v>
+        <v>8.420427553444181</v>
       </c>
       <c r="W7">
-        <v>0.07314285714285713</v>
+        <v>0.0485947416137806</v>
       </c>
       <c r="X7">
-        <v>0.1919520292914943</v>
+        <v>0.1662200077199834</v>
       </c>
       <c r="Y7">
-        <v>-0.1188091721486371</v>
+        <v>-0.1176252661062028</v>
       </c>
       <c r="Z7">
-        <v>0.08352895430390138</v>
+        <v>0.1239870340356564</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03936244389050374</v>
+        <v>0.05447999781980395</v>
       </c>
       <c r="AC7">
-        <v>-0.03936244389050374</v>
+        <v>-0.05447999781980395</v>
       </c>
       <c r="AD7">
-        <v>104.6</v>
+        <v>53.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>104.6</v>
+        <v>53.5</v>
       </c>
       <c r="AG7">
-        <v>104.111</v>
+        <v>-17.40000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.8782535684298909</v>
+        <v>0.8640180878552971</v>
       </c>
       <c r="AI7">
-        <v>0.6308805790108564</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="AJ7">
-        <v>0.8777516419219128</v>
+        <v>1.937639198218262</v>
       </c>
       <c r="AK7">
-        <v>0.6297887012963445</v>
+        <v>-0.2205323193916351</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1308,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aasen Sparebank (OB:AASB)</t>
+          <t>Totens Sparebank (OB:TOTG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1317,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.06269999999999999</v>
+        <v>0.0479</v>
       </c>
       <c r="E8">
-        <v>0.09329999999999999</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1335,28 +1338,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>4.76</v>
+        <v>21.9</v>
       </c>
       <c r="L8">
-        <v>0.3661538461538462</v>
+        <v>0.4866666666666666</v>
       </c>
       <c r="M8">
-        <v>0.6948799999999999</v>
+        <v>6.94</v>
       </c>
       <c r="N8">
-        <v>0.04211393939393939</v>
+        <v>0.05073099415204678</v>
       </c>
       <c r="O8">
-        <v>0.1459831932773109</v>
+        <v>0.3168949771689498</v>
       </c>
       <c r="P8">
-        <v>0.6948799999999999</v>
+        <v>6.94</v>
       </c>
       <c r="Q8">
-        <v>0.04211393939393939</v>
+        <v>0.05073099415204678</v>
       </c>
       <c r="R8">
-        <v>0.1459831932773109</v>
+        <v>0.3168949771689498</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1365,55 +1368,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1.05</v>
+        <v>24</v>
       </c>
       <c r="V8">
-        <v>0.06363636363636364</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="W8">
-        <v>0.08702010968921388</v>
+        <v>0.08909682668836451</v>
       </c>
       <c r="X8">
-        <v>0.1875016483196057</v>
+        <v>0.1598507011858649</v>
       </c>
       <c r="Y8">
-        <v>-0.1004815386303918</v>
+        <v>-0.07075387449750035</v>
       </c>
       <c r="Z8">
-        <v>0.09772231827407352</v>
+        <v>0.03819061359585844</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03937142795489611</v>
+        <v>0.05452922407446667</v>
       </c>
       <c r="AC8">
-        <v>-0.03937142795489611</v>
+        <v>-0.05452922407446667</v>
       </c>
       <c r="AD8">
-        <v>115.5</v>
+        <v>817</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>115.5</v>
+        <v>817</v>
       </c>
       <c r="AG8">
-        <v>114.45</v>
+        <v>793</v>
       </c>
       <c r="AH8">
-        <v>0.875</v>
+        <v>0.8565737051792829</v>
       </c>
       <c r="AI8">
-        <v>0.64453125</v>
+        <v>0.7899825952426996</v>
       </c>
       <c r="AJ8">
-        <v>0.8739977090492556</v>
+        <v>0.8528715852871586</v>
       </c>
       <c r="AK8">
-        <v>0.6424361493123772</v>
+        <v>0.7849930706790734</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1430,7 +1433,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandnes Sparebank (OB:SADG)</t>
+          <t>SpareBank 1 Nordmøre (OB:SNOR)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1439,10 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.139</v>
+        <v>0.103</v>
       </c>
       <c r="E9">
-        <v>0.455</v>
+        <v>0.0629</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1457,28 +1460,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>30.4</v>
+        <v>21.5</v>
       </c>
       <c r="L9">
-        <v>0.4158686730506156</v>
+        <v>0.3041018387553041</v>
       </c>
       <c r="M9">
-        <v>14.2538</v>
+        <v>5.47</v>
       </c>
       <c r="N9">
-        <v>0.06073199829569664</v>
+        <v>0.04756521739130434</v>
       </c>
       <c r="O9">
-        <v>0.468875</v>
+        <v>0.2544186046511628</v>
       </c>
       <c r="P9">
-        <v>14.2538</v>
+        <v>5.47</v>
       </c>
       <c r="Q9">
-        <v>0.06073199829569664</v>
+        <v>0.04756521739130434</v>
       </c>
       <c r="R9">
-        <v>0.468875</v>
+        <v>0.2544186046511628</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1487,55 +1490,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>63.4</v>
+        <v>105</v>
       </c>
       <c r="V9">
-        <v>0.2701320835108649</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="W9">
-        <v>0.09819121447028423</v>
+        <v>0.05683320116309807</v>
       </c>
       <c r="X9">
-        <v>0.1796256906256329</v>
+        <v>0.1505343006495951</v>
       </c>
       <c r="Y9">
-        <v>-0.08143447615534866</v>
+        <v>-0.09370109948649707</v>
       </c>
       <c r="Z9">
-        <v>0.04143990929705215</v>
+        <v>0.07801551482515476</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03938856256013493</v>
+        <v>0.05461178006331811</v>
       </c>
       <c r="AC9">
-        <v>-0.03938856256013493</v>
+        <v>-0.05461178006331811</v>
       </c>
       <c r="AD9">
-        <v>1554.1</v>
+        <v>622.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1554.1</v>
+        <v>622.6</v>
       </c>
       <c r="AG9">
-        <v>1490.7</v>
+        <v>517.6</v>
       </c>
       <c r="AH9">
-        <v>0.8687947227191413</v>
+        <v>0.8440889370932755</v>
       </c>
       <c r="AI9">
-        <v>0.8113709930040722</v>
+        <v>0.641921847613156</v>
       </c>
       <c r="AJ9">
-        <v>0.8639735713457749</v>
+        <v>0.8182105595953209</v>
       </c>
       <c r="AK9">
-        <v>0.8049136069114471</v>
+        <v>0.5984506879408024</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1552,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Totens Sparebank (OB:TOTG)</t>
+          <t>SpareBank 1 SR-Bank ASA (OB:SRBNK)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,10 +1564,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0578</v>
+        <v>0.08539999999999999</v>
       </c>
       <c r="E10">
-        <v>0.104</v>
+        <v>0.108</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1579,28 +1582,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>22.9</v>
+        <v>300.8</v>
       </c>
       <c r="L10">
-        <v>0.4525691699604742</v>
+        <v>0.4743731272669926</v>
       </c>
       <c r="M10">
-        <v>6.25</v>
+        <v>221.6</v>
       </c>
       <c r="N10">
-        <v>0.04161118508655127</v>
+        <v>0.07073318650451658</v>
       </c>
       <c r="O10">
-        <v>0.2729257641921398</v>
+        <v>0.7367021276595744</v>
       </c>
       <c r="P10">
-        <v>6.25</v>
+        <v>221.6</v>
       </c>
       <c r="Q10">
-        <v>0.04161118508655127</v>
+        <v>0.07073318650451658</v>
       </c>
       <c r="R10">
-        <v>0.2729257641921398</v>
+        <v>0.7367021276595744</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1609,55 +1612,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>23.1</v>
+        <v>121.6</v>
       </c>
       <c r="V10">
-        <v>0.1537949400798935</v>
+        <v>0.03881387851511379</v>
       </c>
       <c r="W10">
-        <v>0.1101491101491101</v>
+        <v>0.09959275568652121</v>
       </c>
       <c r="X10">
-        <v>0.1742246752341487</v>
+        <v>0.1387820625362035</v>
       </c>
       <c r="Y10">
-        <v>-0.06407556508503856</v>
+        <v>-0.0391893068496823</v>
       </c>
       <c r="Z10">
-        <v>0.05620348772631346</v>
+        <v>0.03479439426696371</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03940133075427725</v>
+        <v>0.05473894994435685</v>
       </c>
       <c r="AC10">
-        <v>-0.03940133075427725</v>
+        <v>-0.05473894994435685</v>
       </c>
       <c r="AD10">
-        <v>955.6</v>
+        <v>14754.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>955.6</v>
+        <v>14754.8</v>
       </c>
       <c r="AG10">
-        <v>932.5</v>
+        <v>14633.2</v>
       </c>
       <c r="AH10">
-        <v>0.8641707361186471</v>
+        <v>0.8248573041810853</v>
       </c>
       <c r="AI10">
-        <v>0.7954053604128516</v>
+        <v>0.8512548318236889</v>
       </c>
       <c r="AJ10">
-        <v>0.8612727440657615</v>
+        <v>0.8236585407039249</v>
       </c>
       <c r="AK10">
-        <v>0.7913943817364</v>
+        <v>0.8502039346014851</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1674,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aurskog Sparebank (OB:AURG)</t>
+          <t>Sparebank 68° Nord (OB:SB68)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1683,10 +1686,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0694</v>
+        <v>0.252</v>
       </c>
       <c r="E11">
-        <v>0.09369999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1701,28 +1704,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>15</v>
+        <v>10.2</v>
       </c>
       <c r="L11">
-        <v>0.4716981132075472</v>
+        <v>0.3908045977011494</v>
       </c>
       <c r="M11">
-        <v>2.21</v>
+        <v>2.18889</v>
       </c>
       <c r="N11">
-        <v>0.02522831050228311</v>
+        <v>0.04225656370656371</v>
       </c>
       <c r="O11">
-        <v>0.1473333333333333</v>
+        <v>0.2145970588235294</v>
       </c>
       <c r="P11">
-        <v>2.21</v>
+        <v>2.18889</v>
       </c>
       <c r="Q11">
-        <v>0.02522831050228311</v>
+        <v>0.04225656370656371</v>
       </c>
       <c r="R11">
-        <v>0.1473333333333333</v>
+        <v>0.2145970588235294</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1731,55 +1734,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>88</v>
+        <v>7.02</v>
       </c>
       <c r="V11">
-        <v>1.004566210045662</v>
+        <v>0.1355212355212355</v>
       </c>
       <c r="W11">
-        <v>0.1033057851239669</v>
+        <v>0.07088255733148019</v>
       </c>
       <c r="X11">
-        <v>0.1437541542652234</v>
+        <v>0.1249111217336028</v>
       </c>
       <c r="Y11">
-        <v>-0.04044836914125642</v>
+        <v>-0.05402856440212259</v>
       </c>
       <c r="Z11">
-        <v>0.07475317348377998</v>
+        <v>0.06867336736304794</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03949440902017184</v>
+        <v>0.05493629088168034</v>
       </c>
       <c r="AC11">
-        <v>-0.03949440902017184</v>
+        <v>-0.05493629088168034</v>
       </c>
       <c r="AD11">
-        <v>429.1</v>
+        <v>200.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>429.1</v>
+        <v>200.9</v>
       </c>
       <c r="AG11">
-        <v>341.1</v>
+        <v>193.88</v>
       </c>
       <c r="AH11">
-        <v>0.830462550803174</v>
+        <v>0.7950138504155125</v>
       </c>
       <c r="AI11">
-        <v>0.7140955233815942</v>
+        <v>0.6187249769017555</v>
       </c>
       <c r="AJ11">
-        <v>0.7956613016095171</v>
+        <v>0.789156626506024</v>
       </c>
       <c r="AK11">
-        <v>0.6650419185026321</v>
+        <v>0.6102996726265424</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1796,7 +1799,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SpareBank 1 Nordmøre (OB:SNOR)</t>
+          <t>Aurskog Sparebank (OB:AURG)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1805,10 +1808,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.061</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="E12">
-        <v>-0.0165</v>
+        <v>0.113</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1823,28 +1826,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>15</v>
+        <v>13.7</v>
       </c>
       <c r="L12">
-        <v>0.24</v>
+        <v>0.4581939799331103</v>
       </c>
       <c r="M12">
-        <v>2.99</v>
+        <v>4.59</v>
       </c>
       <c r="N12">
-        <v>0.02201767304860088</v>
+        <v>0.04447674418604651</v>
       </c>
       <c r="O12">
-        <v>0.1993333333333333</v>
+        <v>0.335036496350365</v>
       </c>
       <c r="P12">
-        <v>2.99</v>
+        <v>4.59</v>
       </c>
       <c r="Q12">
-        <v>0.02201767304860088</v>
+        <v>0.04447674418604651</v>
       </c>
       <c r="R12">
-        <v>0.1993333333333333</v>
+        <v>0.335036496350365</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1853,55 +1856,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>112.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="V12">
-        <v>0.8269513991163475</v>
+        <v>0.6695736434108527</v>
       </c>
       <c r="W12">
-        <v>0.06167763157894737</v>
+        <v>0.07974388824214201</v>
       </c>
       <c r="X12">
-        <v>0.142006233927901</v>
+        <v>0.1193248153454883</v>
       </c>
       <c r="Y12">
-        <v>-0.08032860234895359</v>
+        <v>-0.03958092710334632</v>
       </c>
       <c r="Z12">
-        <v>0.1048956917241495</v>
+        <v>0.05829596412556053</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0395011696837084</v>
+        <v>0.05503616281436212</v>
       </c>
       <c r="AC12">
-        <v>-0.0395011696837084</v>
+        <v>-0.05503616281436212</v>
       </c>
       <c r="AD12">
-        <v>653.8</v>
+        <v>365.7</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>653.8</v>
+        <v>365.7</v>
       </c>
       <c r="AG12">
-        <v>541.5</v>
+        <v>296.6</v>
       </c>
       <c r="AH12">
-        <v>0.8280141843971631</v>
+        <v>0.7799104286628279</v>
       </c>
       <c r="AI12">
-        <v>0.6334657494428835</v>
+        <v>0.6853448275862069</v>
       </c>
       <c r="AJ12">
-        <v>0.7994980067916728</v>
+        <v>0.7418709354677339</v>
       </c>
       <c r="AK12">
-        <v>0.5887149380300065</v>
+        <v>0.6385360602798709</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1918,7 +1921,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SpareBank 1 Helgeland (OB:HELG)</t>
+          <t>SpareBank 1 SMN (OB:MING)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1927,10 +1930,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0354</v>
+        <v>0.0733</v>
       </c>
       <c r="E13">
-        <v>-0.0205</v>
+        <v>0.0824</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1945,85 +1948,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>36.8</v>
+        <v>237.7</v>
       </c>
       <c r="L13">
-        <v>0.4039517014270033</v>
+        <v>0.408068669527897</v>
       </c>
       <c r="M13">
-        <v>7.45</v>
+        <v>133.14</v>
       </c>
       <c r="N13">
-        <v>0.02400902352562037</v>
+        <v>0.0796339493988875</v>
       </c>
       <c r="O13">
-        <v>0.2024456521739131</v>
+        <v>0.5601177955405975</v>
       </c>
       <c r="P13">
-        <v>7.45</v>
+        <v>131.3</v>
       </c>
       <c r="Q13">
-        <v>0.02400902352562037</v>
+        <v>0.078533405107961</v>
       </c>
       <c r="R13">
-        <v>0.2024456521739131</v>
+        <v>0.5523769457299117</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.840000000000003</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.01382003905663214</v>
       </c>
       <c r="U13">
-        <v>178.8</v>
+        <v>29.2</v>
       </c>
       <c r="V13">
-        <v>0.5762165646148888</v>
+        <v>0.01746515939948561</v>
       </c>
       <c r="W13">
-        <v>0.09332995181334008</v>
+        <v>0.09329617709396341</v>
       </c>
       <c r="X13">
-        <v>0.129285781460924</v>
+        <v>0.1131052861781472</v>
       </c>
       <c r="Y13">
-        <v>-0.03595582964758393</v>
+        <v>-0.01980910908418382</v>
       </c>
       <c r="Z13">
-        <v>0.06113273386122667</v>
+        <v>0.07096648432645802</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03955694235286752</v>
+        <v>0.05516621679280174</v>
       </c>
       <c r="AC13">
-        <v>-0.03955694235286752</v>
+        <v>-0.05516621679280174</v>
       </c>
       <c r="AD13">
-        <v>1304.3</v>
+        <v>5301.4</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1304.3</v>
+        <v>5301.4</v>
       </c>
       <c r="AG13">
-        <v>1125.5</v>
+        <v>5272.2</v>
       </c>
       <c r="AH13">
-        <v>0.8078161773813948</v>
+        <v>0.760242639783173</v>
       </c>
       <c r="AI13">
-        <v>0.7293518984510429</v>
+        <v>0.7069947322797893</v>
       </c>
       <c r="AJ13">
-        <v>0.7838835492408414</v>
+        <v>0.7592344580291182</v>
       </c>
       <c r="AK13">
-        <v>0.6992854923889407</v>
+        <v>0.7058492763712798</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2040,7 +2043,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Romsdal Sparebank (OB:ROMSB)</t>
+          <t>Jæren Sparebank (OB:JAREN)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2048,6 +2051,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.0507</v>
+      </c>
+      <c r="E14">
+        <v>0.0554</v>
+      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2061,28 +2070,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>4.48</v>
+        <v>17.2</v>
       </c>
       <c r="L14">
-        <v>0.256</v>
+        <v>0.4751381215469613</v>
       </c>
       <c r="M14">
-        <v>0.7546</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N14">
-        <v>0.02647719298245614</v>
+        <v>0.08031959629941127</v>
       </c>
       <c r="O14">
-        <v>0.1684375</v>
+        <v>0.555232558139535</v>
       </c>
       <c r="P14">
-        <v>0.7546</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q14">
-        <v>0.02647719298245614</v>
+        <v>0.08031959629941127</v>
       </c>
       <c r="R14">
-        <v>0.1684375</v>
+        <v>0.555232558139535</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2091,55 +2100,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1.26</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="V14">
-        <v>0.04421052631578947</v>
+        <v>0.06753574432296046</v>
       </c>
       <c r="W14">
-        <v>0.05621079046424091</v>
+        <v>0.07248209018120522</v>
       </c>
       <c r="X14">
-        <v>0.1265865865278128</v>
+        <v>0.10560842492993</v>
       </c>
       <c r="Y14">
-        <v>-0.07037579606357189</v>
+        <v>-0.0331263347487248</v>
       </c>
       <c r="Z14">
-        <v>0.08202484180923364</v>
+        <v>0.05833158768268904</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.03957050476872153</v>
+        <v>0.05535760480038119</v>
       </c>
       <c r="AC14">
-        <v>-0.03957050476872153</v>
+        <v>-0.05535760480038119</v>
       </c>
       <c r="AD14">
-        <v>116.1</v>
+        <v>323.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>116.1</v>
+        <v>323.6</v>
       </c>
       <c r="AG14">
-        <v>114.84</v>
+        <v>315.5700000000001</v>
       </c>
       <c r="AH14">
-        <v>0.8029045643153527</v>
+        <v>0.7312994350282487</v>
       </c>
       <c r="AI14">
-        <v>0.5600578871201157</v>
+        <v>0.6119515885022694</v>
       </c>
       <c r="AJ14">
-        <v>0.8011720385098369</v>
+        <v>0.7263332335949548</v>
       </c>
       <c r="AK14">
-        <v>0.5573675014560279</v>
+        <v>0.6059680857192236</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2156,7 +2165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SpareBank 1 SR-Bank ASA (OB:SRBNK)</t>
+          <t>SpareBank 1 Helgeland (OB:HELG)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2165,10 +2174,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0882</v>
+        <v>0.0555</v>
       </c>
       <c r="E15">
-        <v>0.102</v>
+        <v>0.008369999999999999</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2183,28 +2192,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>329.6</v>
+        <v>27.1</v>
       </c>
       <c r="L15">
-        <v>0.4747227423304048</v>
+        <v>0.3533246414602347</v>
       </c>
       <c r="M15">
-        <v>169.3</v>
+        <v>9.94</v>
       </c>
       <c r="N15">
-        <v>0.04378976773058818</v>
+        <v>0.03024034073623365</v>
       </c>
       <c r="O15">
-        <v>0.5136529126213593</v>
+        <v>0.3667896678966789</v>
       </c>
       <c r="P15">
-        <v>169.3</v>
+        <v>9.94</v>
       </c>
       <c r="Q15">
-        <v>0.04378976773058818</v>
+        <v>0.03024034073623365</v>
       </c>
       <c r="R15">
-        <v>0.5136529126213593</v>
+        <v>0.3667896678966789</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2213,55 +2222,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>241.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V15">
-        <v>0.06241270498163572</v>
+        <v>0.2467295406145421</v>
       </c>
       <c r="W15">
-        <v>0.119810977826245</v>
+        <v>0.0560264626834815</v>
       </c>
       <c r="X15">
-        <v>0.1249472242030566</v>
+        <v>0.1028470145780647</v>
       </c>
       <c r="Y15">
-        <v>-0.005136246376811593</v>
+        <v>-0.04682055189458317</v>
       </c>
       <c r="Z15">
-        <v>0.03975447617193539</v>
+        <v>0.04766343524732786</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03957908564195774</v>
+        <v>0.05544028787048495</v>
       </c>
       <c r="AC15">
-        <v>-0.03957908564195774</v>
+        <v>-0.05544028787048495</v>
       </c>
       <c r="AD15">
-        <v>15445.2</v>
+        <v>840.2</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>15445.2</v>
+        <v>840.2</v>
       </c>
       <c r="AG15">
-        <v>15203.9</v>
+        <v>759.1</v>
       </c>
       <c r="AH15">
-        <v>0.7997970110918939</v>
+        <v>0.7187954487124647</v>
       </c>
       <c r="AI15">
-        <v>0.836435514879099</v>
+        <v>0.6566114410753361</v>
       </c>
       <c r="AJ15">
-        <v>0.7972637794243345</v>
+        <v>0.6978304835447693</v>
       </c>
       <c r="AK15">
-        <v>0.8342698170564414</v>
+        <v>0.633375052148519</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2278,7 +2287,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grong Sparebank (OB:GRONG)</t>
+          <t>SpareBank 1 Sørøst-Norge (OB:SOON)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2286,6 +2295,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.151</v>
+      </c>
+      <c r="E16">
+        <v>0.167</v>
+      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2299,28 +2314,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>11.9</v>
+        <v>84.7</v>
       </c>
       <c r="L16">
-        <v>0.4507575757575758</v>
+        <v>0.4178589047853972</v>
       </c>
       <c r="M16">
-        <v>2.04336</v>
+        <v>45.7</v>
       </c>
       <c r="N16">
-        <v>0.04204444444444444</v>
+        <v>0.0584473717866735</v>
       </c>
       <c r="O16">
-        <v>0.1717109243697479</v>
+        <v>0.539551357733176</v>
       </c>
       <c r="P16">
-        <v>2.04336</v>
+        <v>45.7</v>
       </c>
       <c r="Q16">
-        <v>0.04204444444444444</v>
+        <v>0.0584473717866735</v>
       </c>
       <c r="R16">
-        <v>0.1717109243697479</v>
+        <v>0.539551357733176</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2329,55 +2344,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.463</v>
+        <v>111.7</v>
       </c>
       <c r="V16">
-        <v>0.009526748971193415</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="W16">
-        <v>0.1401648998822144</v>
+        <v>0.07475068396434562</v>
       </c>
       <c r="X16">
-        <v>0.1156725703274847</v>
+        <v>0.09995017602198857</v>
       </c>
       <c r="Y16">
-        <v>0.02449232955472969</v>
+        <v>-0.02519949205764295</v>
       </c>
       <c r="Z16">
-        <v>0.1230648747675053</v>
+        <v>0.07011414735385679</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03963322650903595</v>
+        <v>0.05553572112507292</v>
       </c>
       <c r="AC16">
-        <v>-0.03963322650903595</v>
+        <v>-0.05553572112507292</v>
       </c>
       <c r="AD16">
-        <v>172.5</v>
+        <v>1862.9</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>172.5</v>
+        <v>1862.9</v>
       </c>
       <c r="AG16">
-        <v>172.037</v>
+        <v>1751.2</v>
       </c>
       <c r="AH16">
-        <v>0.7801899592944369</v>
+        <v>0.7043632788868723</v>
       </c>
       <c r="AI16">
-        <v>0.6227436823104693</v>
+        <v>0.6198096885813148</v>
       </c>
       <c r="AJ16">
-        <v>0.7797286946432376</v>
+        <v>0.6913268327345941</v>
       </c>
       <c r="AK16">
-        <v>0.6221120501054108</v>
+        <v>0.605134939009641</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2394,7 +2409,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jæren Sparebank (OB:JAREN)</t>
+          <t>SpareBank 1 Nord-Norge (OB:NONG)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2403,10 +2418,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0371</v>
+        <v>0.0675</v>
       </c>
       <c r="E17">
-        <v>0.0265</v>
+        <v>0.0788</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2421,28 +2436,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>14.5</v>
+        <v>172.7</v>
       </c>
       <c r="L17">
-        <v>0.3502415458937198</v>
+        <v>0.4560337998415632</v>
       </c>
       <c r="M17">
-        <v>4.24</v>
+        <v>224</v>
       </c>
       <c r="N17">
-        <v>0.03648881239242685</v>
+        <v>0.2289686190330165</v>
       </c>
       <c r="O17">
-        <v>0.2924137931034483</v>
+        <v>1.297046902142444</v>
       </c>
       <c r="P17">
-        <v>4.24</v>
+        <v>224</v>
       </c>
       <c r="Q17">
-        <v>0.03648881239242685</v>
+        <v>0.2289686190330165</v>
       </c>
       <c r="R17">
-        <v>0.2924137931034483</v>
+        <v>1.297046902142444</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2451,55 +2466,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>8.81</v>
+        <v>11</v>
       </c>
       <c r="V17">
-        <v>0.07581755593803786</v>
+        <v>0.01124399468465706</v>
       </c>
       <c r="W17">
-        <v>0.0703883495145631</v>
+        <v>0.09078006728343145</v>
       </c>
       <c r="X17">
-        <v>0.1120291320791922</v>
+        <v>0.09546882380932897</v>
       </c>
       <c r="Y17">
-        <v>-0.04164078256462905</v>
+        <v>-0.004688756525897522</v>
       </c>
       <c r="Z17">
-        <v>0.07475083056478404</v>
+        <v>0.0819732455950474</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.03965751241842994</v>
+        <v>0.05570431713913686</v>
       </c>
       <c r="AC17">
-        <v>-0.03965751241842994</v>
+        <v>-0.05570431713913686</v>
       </c>
       <c r="AD17">
-        <v>392.1</v>
+        <v>2068.1</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>392.1</v>
+        <v>2068.1</v>
       </c>
       <c r="AG17">
-        <v>383.29</v>
+        <v>2057.1</v>
       </c>
       <c r="AH17">
-        <v>0.7713948455636436</v>
+        <v>0.6788668592436975</v>
       </c>
       <c r="AI17">
-        <v>0.6229742612011439</v>
+        <v>0.5882135441849883</v>
       </c>
       <c r="AJ17">
-        <v>0.7673627099641634</v>
+        <v>0.6777031033801147</v>
       </c>
       <c r="AK17">
-        <v>0.6176219404115438</v>
+        <v>0.5869211675083454</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2516,7 +2531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SpareBank 1 SMN (OB:MING)</t>
+          <t>Grong Sparebank (OB:GRONG)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2524,15 +2539,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.105</v>
-      </c>
-      <c r="E18">
-        <v>0.115</v>
-      </c>
-      <c r="F18">
-        <v>0.186</v>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2546,85 +2552,85 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>286.2</v>
+        <v>12.8</v>
       </c>
       <c r="L18">
-        <v>0.3933479934029686</v>
+        <v>0.5059288537549407</v>
       </c>
       <c r="M18">
-        <v>26.458</v>
+        <v>3.29113</v>
       </c>
       <c r="N18">
-        <v>0.0120901114969841</v>
+        <v>0.05134368174726989</v>
       </c>
       <c r="O18">
-        <v>0.09244584206848358</v>
+        <v>0.25711953125</v>
       </c>
       <c r="P18">
-        <v>26</v>
+        <v>3.29113</v>
       </c>
       <c r="Q18">
-        <v>0.01188082617437397</v>
+        <v>0.05134368174726989</v>
       </c>
       <c r="R18">
-        <v>0.09084556254367575</v>
+        <v>0.25711953125</v>
       </c>
       <c r="S18">
-        <v>0.4579999999999984</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>0.01731045430493607</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>138.2</v>
+        <v>6.95</v>
       </c>
       <c r="V18">
-        <v>0.06315116066532626</v>
+        <v>0.1084243369734789</v>
       </c>
       <c r="W18">
-        <v>0.1338258673898812</v>
+        <v>0.122488038277512</v>
       </c>
       <c r="X18">
-        <v>0.0969435224069147</v>
+        <v>0.09262980521377664</v>
       </c>
       <c r="Y18">
-        <v>0.03688234498296653</v>
+        <v>0.02985823306373532</v>
       </c>
       <c r="Z18">
-        <v>0.0921129256867958</v>
+        <v>0.09148866155342686</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.03978285734385649</v>
+        <v>0.05582704247060458</v>
       </c>
       <c r="AC18">
-        <v>-0.03978285734385649</v>
+        <v>-0.05582704247060458</v>
       </c>
       <c r="AD18">
-        <v>5798.5</v>
+        <v>124.6</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>5798.5</v>
+        <v>124.6</v>
       </c>
       <c r="AG18">
-        <v>5660.3</v>
+        <v>117.65</v>
       </c>
       <c r="AH18">
-        <v>0.7260013271732462</v>
+        <v>0.6603073661897192</v>
       </c>
       <c r="AI18">
-        <v>0.6867412802747676</v>
+        <v>0.5498676081200353</v>
       </c>
       <c r="AJ18">
-        <v>0.7211767553862423</v>
+        <v>0.6473177441540577</v>
       </c>
       <c r="AK18">
-        <v>0.6815286624203822</v>
+        <v>0.535624857728204</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2650,10 +2656,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0461</v>
+        <v>0.0815</v>
       </c>
       <c r="E19">
-        <v>0.0634</v>
+        <v>0.215</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2668,28 +2674,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>4.39</v>
+        <v>4.52</v>
       </c>
       <c r="L19">
-        <v>0.356910569105691</v>
+        <v>0.4224299065420561</v>
       </c>
       <c r="M19">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="N19">
-        <v>0.05603960396039604</v>
+        <v>0.04064386317907445</v>
       </c>
       <c r="O19">
-        <v>0.6446469248291572</v>
+        <v>0.4469026548672567</v>
       </c>
       <c r="P19">
-        <v>2.83</v>
+        <v>2.02</v>
       </c>
       <c r="Q19">
-        <v>0.05603960396039604</v>
+        <v>0.04064386317907445</v>
       </c>
       <c r="R19">
-        <v>0.6446469248291572</v>
+        <v>0.4469026548672567</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2698,55 +2704,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>29.2</v>
+        <v>18.5</v>
       </c>
       <c r="V19">
-        <v>0.5782178217821782</v>
+        <v>0.3722334004024145</v>
       </c>
       <c r="W19">
-        <v>0.0693522906793049</v>
+        <v>0.06484935437589669</v>
       </c>
       <c r="X19">
-        <v>0.09450844336756457</v>
+        <v>0.0923918464508733</v>
       </c>
       <c r="Y19">
-        <v>-0.02515615268825967</v>
+        <v>-0.02754249207497661</v>
       </c>
       <c r="Z19">
-        <v>0.06169433716206048</v>
+        <v>0.06353919239904987</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03980791078940279</v>
+        <v>0.05583797643275003</v>
       </c>
       <c r="AC19">
-        <v>-0.03980791078940279</v>
+        <v>-0.05583797643275003</v>
       </c>
       <c r="AD19">
-        <v>127.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>127.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AG19">
-        <v>98.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AH19">
-        <v>0.7169282511210763</v>
+        <v>0.6586538461538461</v>
       </c>
       <c r="AI19">
-        <v>0.6472672064777327</v>
+        <v>0.6203104786545924</v>
       </c>
       <c r="AJ19">
-        <v>0.6615281501340483</v>
+        <v>0.6089693154996066</v>
       </c>
       <c r="AK19">
-        <v>0.586104513064133</v>
+        <v>0.5686994856722998</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2763,7 +2769,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SpareBank 1 Sørøst-Norge (OB:SOON)</t>
+          <t>SpareBank 1 Østfold Akershus (OB:SOAG)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2772,10 +2778,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.152</v>
+        <v>0.0573</v>
       </c>
       <c r="E20">
-        <v>0.188</v>
+        <v>0.0505</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2790,85 +2796,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>86</v>
+        <v>35.8</v>
       </c>
       <c r="L20">
-        <v>0.4516806722689076</v>
+        <v>0.4323671497584541</v>
       </c>
       <c r="M20">
-        <v>26.6</v>
+        <v>24.46</v>
       </c>
       <c r="N20">
-        <v>0.03023758099352052</v>
+        <v>0.06158106747230615</v>
       </c>
       <c r="O20">
-        <v>0.3093023255813954</v>
+        <v>0.6832402234636872</v>
       </c>
       <c r="P20">
-        <v>15.1</v>
+        <v>24</v>
       </c>
       <c r="Q20">
-        <v>0.01716494259406616</v>
+        <v>0.06042296072507553</v>
       </c>
       <c r="R20">
-        <v>0.1755813953488372</v>
+        <v>0.670391061452514</v>
       </c>
       <c r="S20">
-        <v>11.5</v>
+        <v>0.4600000000000009</v>
       </c>
       <c r="T20">
-        <v>0.4323308270676692</v>
+        <v>0.01880621422730993</v>
       </c>
       <c r="U20">
-        <v>187.7</v>
+        <v>141</v>
       </c>
       <c r="V20">
-        <v>0.2133681937023985</v>
+        <v>0.3549848942598187</v>
       </c>
       <c r="W20">
-        <v>0.1484550319350941</v>
+        <v>0.07755632582322355</v>
       </c>
       <c r="X20">
-        <v>0.08791848485464414</v>
+        <v>0.07433848958645622</v>
       </c>
       <c r="Y20">
-        <v>0.06053654708044996</v>
+        <v>0.00321783623676733</v>
       </c>
       <c r="Z20">
-        <v>0.1392250488092018</v>
+        <v>0.1063174114021572</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.03988485209710475</v>
+        <v>0.05715963736713505</v>
       </c>
       <c r="AC20">
-        <v>-0.03988485209710475</v>
+        <v>-0.05715963736713505</v>
       </c>
       <c r="AD20">
-        <v>1949.5</v>
+        <v>336.7</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>1949.5</v>
+        <v>336.7</v>
       </c>
       <c r="AG20">
-        <v>1761.8</v>
+        <v>195.7</v>
       </c>
       <c r="AH20">
-        <v>0.6890640463735332</v>
+        <v>0.4587818503883363</v>
       </c>
       <c r="AI20">
-        <v>0.6321950903135843</v>
+        <v>0.468941504178273</v>
       </c>
       <c r="AJ20">
-        <v>0.6669695248911603</v>
+        <v>0.3300725248777197</v>
       </c>
       <c r="AK20">
-        <v>0.6083563535911602</v>
+        <v>0.3391681109185442</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2885,7 +2891,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SpareBank 1 Nord-Norge (OB:NONG)</t>
+          <t>Kraft Bank ASA (OB:KRAB)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2893,15 +2899,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.0819</v>
-      </c>
-      <c r="E21">
-        <v>0.118</v>
-      </c>
-      <c r="F21">
-        <v>0.099</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2915,28 +2912,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>224</v>
+        <v>4.38</v>
       </c>
       <c r="L21">
-        <v>0.4865334491746308</v>
+        <v>0.3395348837209302</v>
       </c>
       <c r="M21">
-        <v>44.87880000000001</v>
+        <v>0.967</v>
       </c>
       <c r="N21">
-        <v>0.03497412718204489</v>
+        <v>0.0256498673740053</v>
       </c>
       <c r="O21">
-        <v>0.2003517857142857</v>
+        <v>0.2207762557077625</v>
       </c>
       <c r="P21">
-        <v>44.87880000000001</v>
+        <v>0.967</v>
       </c>
       <c r="Q21">
-        <v>0.03497412718204489</v>
+        <v>0.0256498673740053</v>
       </c>
       <c r="R21">
-        <v>0.2003517857142857</v>
+        <v>0.2207762557077625</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2945,55 +2942,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>69.5</v>
+        <v>7.13</v>
       </c>
       <c r="V21">
-        <v>0.05416147132169576</v>
+        <v>0.1891246684350132</v>
       </c>
       <c r="W21">
-        <v>0.1430578617958871</v>
+        <v>0.1081481481481481</v>
       </c>
       <c r="X21">
-        <v>0.08699714797410583</v>
+        <v>0.06033808632550555</v>
       </c>
       <c r="Y21">
-        <v>0.05606071382178125</v>
+        <v>0.04781006182264259</v>
       </c>
       <c r="Z21">
-        <v>0.09670643589312719</v>
+        <v>0.3460578909246989</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.03989683295955167</v>
+        <v>0.06013648703477948</v>
       </c>
       <c r="AC21">
-        <v>-0.03989683295955167</v>
+        <v>-0.06013648703477948</v>
       </c>
       <c r="AD21">
-        <v>2786.9</v>
+        <v>0.327</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>2786.9</v>
+        <v>0.327</v>
       </c>
       <c r="AG21">
-        <v>2717.4</v>
+        <v>-6.803</v>
       </c>
       <c r="AH21">
-        <v>0.6847251910272475</v>
+        <v>0.008599153233229021</v>
       </c>
       <c r="AI21">
-        <v>0.5939178245673856</v>
+        <v>0.009026416760979381</v>
       </c>
       <c r="AJ21">
-        <v>0.6792481127830825</v>
+        <v>-0.2201831893064051</v>
       </c>
       <c r="AK21">
-        <v>0.5878128447511303</v>
+        <v>-0.2338041722514349</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3010,7 +3007,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SpareBank 1 Østfold Akershus (OB:SOAG)</t>
+          <t>Instabank ASA (OB:INSTA)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3019,10 +3016,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.05690000000000001</v>
-      </c>
-      <c r="E22">
-        <v>0.08070000000000001</v>
+        <v>0.351</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3037,85 +3031,82 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>50.7</v>
+        <v>7.58</v>
       </c>
       <c r="L22">
-        <v>0.4810246679316888</v>
+        <v>0.319831223628692</v>
       </c>
       <c r="M22">
-        <v>4.13</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.008440629470672388</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.08145956607495068</v>
+        <v>-0</v>
       </c>
       <c r="P22">
-        <v>4.13</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.008440629470672388</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.08145956607495068</v>
+        <v>-0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>191.9</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>0.3921929286736154</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>0.1304347826086957</v>
+        <v>0.1031292517006803</v>
       </c>
       <c r="X22">
-        <v>0.06344621148529042</v>
+        <v>0.06175367456918252</v>
       </c>
       <c r="Y22">
-        <v>0.06698857112340525</v>
+        <v>0.04137557713149775</v>
       </c>
       <c r="Z22">
-        <v>0.1277111353447231</v>
+        <v>0.2937530986613783</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.04037953319217288</v>
+        <v>0.06014148386967998</v>
       </c>
       <c r="AC22">
-        <v>-0.04037953319217288</v>
+        <v>-0.06014148386967998</v>
       </c>
       <c r="AD22">
-        <v>509.1</v>
+        <v>5.76</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>509.1</v>
+        <v>5.76</v>
       </c>
       <c r="AG22">
-        <v>317.2</v>
+        <v>5.76</v>
       </c>
       <c r="AH22">
-        <v>0.5099158653846153</v>
+        <v>0.08551068883610451</v>
       </c>
       <c r="AI22">
-        <v>0.5244668795714433</v>
+        <v>0.0797121505673955</v>
       </c>
       <c r="AJ22">
-        <v>0.3933044017358959</v>
+        <v>0.08551068883610451</v>
       </c>
       <c r="AK22">
-        <v>0.4072932717000514</v>
+        <v>0.0797121505673955</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3132,7 +3123,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kraft Bank ASA (OB:KRAB)</t>
+          <t>Aprila Bank ASA (OTCNO:APRILA)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3153,10 +3144,10 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>5.05</v>
+        <v>-1.26</v>
       </c>
       <c r="L23">
-        <v>0.3796992481203007</v>
+        <v>-0.2703862660944206</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3165,7 +3156,7 @@
         <v>-0</v>
       </c>
       <c r="O23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3174,61 +3165,61 @@
         <v>-0</v>
       </c>
       <c r="R23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>3.64</v>
+        <v>3.51</v>
       </c>
       <c r="V23">
-        <v>0.06893939393939394</v>
+        <v>0.09023136246786632</v>
       </c>
       <c r="W23">
-        <v>0.153030303030303</v>
+        <v>-0.1305699481865285</v>
       </c>
       <c r="X23">
-        <v>0.0419519631045584</v>
+        <v>0.06019334925228834</v>
       </c>
       <c r="Y23">
-        <v>0.1110783399257446</v>
+        <v>-0.1907632974388168</v>
       </c>
       <c r="Z23">
-        <v>0.4334647850601311</v>
+        <v>1.033259423503326</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.04176592458304957</v>
+        <v>0.06019334925228834</v>
       </c>
       <c r="AC23">
-        <v>-0.04176592458304957</v>
+        <v>-0.06019334925228834</v>
       </c>
       <c r="AD23">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>-3.223</v>
+        <v>-3.51</v>
       </c>
       <c r="AH23">
-        <v>0.007835841930210271</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>0.01019136300315272</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>-0.0650099844686044</v>
+        <v>-0.09918055948007912</v>
       </c>
       <c r="AK23">
-        <v>-0.08646082034498485</v>
+        <v>-0.3054830287206266</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3245,7 +3236,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aprila Bank ASA (OTCNO:APRILA)</t>
+          <t>Tysnes Sparebank (OB:TYSB)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3253,6 +3244,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D24">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="E24">
+        <v>0.143</v>
+      </c>
       <c r="G24">
         <v>0</v>
       </c>
@@ -3266,82 +3263,85 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>-5.07</v>
+        <v>2.83</v>
       </c>
       <c r="L24">
-        <v>-2.069387755102041</v>
+        <v>0.3793565683646113</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>1.2533</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.07080790960451977</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>0.4428621908127208</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>1.2533</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.07080790960451977</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>0.4428621908127208</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
       <c r="U24">
-        <v>5.14</v>
+        <v>6.8</v>
       </c>
       <c r="V24">
-        <v>0.1842293906810036</v>
+        <v>0.384180790960452</v>
       </c>
       <c r="W24">
-        <v>-0.37007299270073</v>
+        <v>0.06388261851015802</v>
       </c>
       <c r="X24">
-        <v>0.04178756165938168</v>
+        <v>0.1077083405407606</v>
       </c>
       <c r="Y24">
-        <v>-0.4118605543601117</v>
+        <v>-0.0438257220306026</v>
       </c>
       <c r="Z24">
-        <v>0.2878965922444184</v>
+        <v>0.05710917344806204</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.04178756165938168</v>
+        <v>0.06193807970002149</v>
       </c>
       <c r="AC24">
-        <v>-0.04178756165938168</v>
+        <v>-0.06193807970002149</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="AG24">
-        <v>-5.14</v>
+        <v>43.6</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>0.7400881057268723</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="AJ24">
-        <v>-0.2258347978910369</v>
+        <v>0.7112561174551387</v>
       </c>
       <c r="AK24">
-        <v>-1.139689578713969</v>
+        <v>0.5165876777251185</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Instabank ASA (OB:INSTA)</t>
+          <t>Romerike Sparebank (OB:ROMER)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3366,6 +3366,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D25">
+        <v>0.0795</v>
+      </c>
+      <c r="E25">
+        <v>0.124</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3379,82 +3385,85 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>8.279999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="L25">
-        <v>0.3221789883268482</v>
+        <v>0.4592274678111588</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>2.414</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.06761904761904761</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>0.225607476635514</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>2.414</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.06761904761904761</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0.225607476635514</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
       <c r="U25">
-        <v>0</v>
+        <v>7.96</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>0.22296918767507</v>
       </c>
       <c r="W25">
-        <v>0.1359605911330049</v>
+        <v>0.07973174366616989</v>
       </c>
       <c r="X25">
-        <v>0.04372861387129339</v>
+        <v>0.1656427857012148</v>
       </c>
       <c r="Y25">
-        <v>0.09223197726171153</v>
+        <v>-0.0859110420350449</v>
       </c>
       <c r="Z25">
-        <v>0.3791678961345529</v>
+        <v>0.04889585602373862</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.04185925985002631</v>
+        <v>0.06222872502691684</v>
       </c>
       <c r="AC25">
-        <v>-0.04185925985002631</v>
+        <v>-0.06222872502691684</v>
       </c>
       <c r="AD25">
-        <v>7.18</v>
+        <v>225.6</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>7.18</v>
+        <v>225.6</v>
       </c>
       <c r="AG25">
-        <v>7.18</v>
+        <v>217.64</v>
       </c>
       <c r="AH25">
-        <v>0.08529341886433832</v>
+        <v>0.8633754305396096</v>
       </c>
       <c r="AI25">
-        <v>0.08899355478433316</v>
+        <v>0.5987261146496816</v>
       </c>
       <c r="AJ25">
-        <v>0.08529341886433832</v>
+        <v>0.8590826557195863</v>
       </c>
       <c r="AK25">
-        <v>0.08899355478433316</v>
+        <v>0.5900661533456241</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3471,7 +3480,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maritime &amp; Merchant Bank ASA (OTCNO:MMBANK)</t>
+          <t>Aasen Sparebank (OB:AASB)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3479,6 +3488,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D26">
+        <v>0.0549</v>
+      </c>
+      <c r="E26">
+        <v>0.07829999999999999</v>
+      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3492,28 +3507,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>6.93</v>
+        <v>3.54</v>
       </c>
       <c r="L26">
-        <v>0.4225609756097561</v>
+        <v>0.3339622641509434</v>
       </c>
       <c r="M26">
-        <v>1.49</v>
+        <v>0.65044</v>
       </c>
       <c r="N26">
-        <v>0.01650055370985604</v>
+        <v>0.05465882352941177</v>
       </c>
       <c r="O26">
-        <v>0.215007215007215</v>
+        <v>0.1837401129943503</v>
       </c>
       <c r="P26">
-        <v>1.49</v>
+        <v>0.65044</v>
       </c>
       <c r="Q26">
-        <v>0.01650055370985604</v>
+        <v>0.05465882352941177</v>
       </c>
       <c r="R26">
-        <v>0.215007215007215</v>
+        <v>0.1837401129943503</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3522,55 +3537,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>84.7</v>
+        <v>6.58</v>
       </c>
       <c r="V26">
-        <v>0.9379844961240311</v>
+        <v>0.5529411764705883</v>
       </c>
       <c r="W26">
-        <v>0.06237623762376238</v>
+        <v>0.05557299843014128</v>
       </c>
       <c r="X26">
-        <v>0.04314073629740654</v>
+        <v>0.1956510029885423</v>
       </c>
       <c r="Y26">
-        <v>0.01923550132635583</v>
+        <v>-0.140078004558401</v>
       </c>
       <c r="Z26">
-        <v>0.1882893226176808</v>
+        <v>0.05950042099354477</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.0419839231212567</v>
+        <v>0.06229225194067885</v>
       </c>
       <c r="AC26">
-        <v>-0.0419839231212567</v>
+        <v>-0.06229225194067885</v>
       </c>
       <c r="AD26">
-        <v>5.87</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>5.87</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AG26">
-        <v>-78.83</v>
+        <v>90.02</v>
       </c>
       <c r="AH26">
-        <v>0.06103774565872933</v>
+        <v>0.8903225806451612</v>
       </c>
       <c r="AI26">
-        <v>0.04789100106061842</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="AJ26">
-        <v>-6.872711421098519</v>
+        <v>0.8832417582417582</v>
       </c>
       <c r="AK26">
-        <v>-2.081594930023765</v>
+        <v>0.6224588576960309</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3587,7 +3602,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sparebank 68° Nord (OB:SB68)</t>
+          <t>Høland og Setskog Sparebank (OB:HSPG)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3595,6 +3610,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D27">
+        <v>0.0415</v>
+      </c>
+      <c r="E27">
+        <v>0.0226</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
@@ -3608,28 +3629,28 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>9.34</v>
+        <v>4.76</v>
       </c>
       <c r="L27">
-        <v>0.3231833910034602</v>
+        <v>0.34</v>
       </c>
       <c r="M27">
-        <v>0.85239</v>
+        <v>0.76</v>
       </c>
       <c r="N27">
-        <v>0.01430184563758389</v>
+        <v>0.06846846846846848</v>
       </c>
       <c r="O27">
-        <v>0.09126231263383297</v>
+        <v>0.1596638655462185</v>
       </c>
       <c r="P27">
-        <v>0.85239</v>
+        <v>0.76</v>
       </c>
       <c r="Q27">
-        <v>0.01430184563758389</v>
+        <v>0.06846846846846848</v>
       </c>
       <c r="R27">
-        <v>0.09126231263383297</v>
+        <v>0.1596638655462185</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3638,182 +3659,60 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>2.14</v>
+        <v>33</v>
       </c>
       <c r="V27">
-        <v>0.03590604026845638</v>
+        <v>2.972972972972973</v>
       </c>
       <c r="W27">
-        <v>0.0758116883116883</v>
+        <v>0.05483870967741936</v>
       </c>
       <c r="X27">
-        <v>0.1250178273619977</v>
+        <v>0.3638632689090948</v>
       </c>
       <c r="Y27">
-        <v>-0.04920613905030935</v>
+        <v>-0.3090245592316754</v>
       </c>
       <c r="Z27">
-        <v>0.07767355605128066</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.04436098544427716</v>
+        <v>0.06242801635331277</v>
       </c>
       <c r="AC27">
-        <v>-0.04436098544427716</v>
+        <v>-0.06242801635331277</v>
       </c>
       <c r="AD27">
-        <v>238.3</v>
+        <v>202</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>238.3</v>
+        <v>202</v>
       </c>
       <c r="AG27">
-        <v>236.16</v>
+        <v>169</v>
       </c>
       <c r="AH27">
-        <v>0.7999328633769721</v>
+        <v>0.9479117785077429</v>
       </c>
       <c r="AI27">
-        <v>0.6234955520669806</v>
+        <v>0.7300325262016625</v>
       </c>
       <c r="AJ27">
-        <v>0.7984852583175547</v>
+        <v>0.9383675735702388</v>
       </c>
       <c r="AK27">
-        <v>0.6213755722780613</v>
+        <v>0.6934755847353303</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Romerike Sparebank (OB:ROMER)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>0.0886</v>
-      </c>
-      <c r="E28">
-        <v>0.0916</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>10.9</v>
-      </c>
-      <c r="L28">
-        <v>0.4022140221402214</v>
-      </c>
-      <c r="M28">
-        <v>0.848</v>
-      </c>
-      <c r="N28">
-        <v>0.04218905472636816</v>
-      </c>
-      <c r="O28">
-        <v>0.07779816513761467</v>
-      </c>
-      <c r="P28">
-        <v>0.848</v>
-      </c>
-      <c r="Q28">
-        <v>0.04218905472636816</v>
-      </c>
-      <c r="R28">
-        <v>0.07779816513761467</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0.415</v>
-      </c>
-      <c r="V28">
-        <v>0.02064676616915423</v>
-      </c>
-      <c r="W28">
-        <v>0.09380378657487091</v>
-      </c>
-      <c r="X28">
-        <v>0.3923505917552297</v>
-      </c>
-      <c r="Y28">
-        <v>-0.2985468051803588</v>
-      </c>
-      <c r="Z28">
-        <v>0.07182613305062285</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0.04482429151522574</v>
-      </c>
-      <c r="AC28">
-        <v>-0.04482429151522574</v>
-      </c>
-      <c r="AD28">
-        <v>338.5</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>338.5</v>
-      </c>
-      <c r="AG28">
-        <v>338.085</v>
-      </c>
-      <c r="AH28">
-        <v>0.9439486893474623</v>
-      </c>
-      <c r="AI28">
-        <v>0.7108357832843343</v>
-      </c>
-      <c r="AJ28">
-        <v>0.9438837472255956</v>
-      </c>
-      <c r="AK28">
-        <v>0.7105835619029603</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/norway/norway_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ27"/>
+  <dimension ref="A1:AQ29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0764</v>
+        <v>0.101</v>
       </c>
       <c r="E2">
-        <v>0.0824</v>
+        <v>0.137</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1105.9</v>
+        <v>1445.61</v>
       </c>
       <c r="L2">
-        <v>0.4310627085347221</v>
+        <v>0.4634078319741499</v>
       </c>
       <c r="M2">
-        <v>781.17696</v>
+        <v>627.84503</v>
       </c>
       <c r="N2">
-        <v>0.08840623705611676</v>
+        <v>0.06593944151891395</v>
       </c>
       <c r="O2">
-        <v>0.7063721493805949</v>
+        <v>0.4343114878840074</v>
       </c>
       <c r="P2">
-        <v>746.7709600000001</v>
+        <v>551.80503</v>
       </c>
       <c r="Q2">
-        <v>0.08451249063513586</v>
+        <v>0.05795333843054801</v>
       </c>
       <c r="R2">
-        <v>0.6752608373270639</v>
+        <v>0.3817108556249611</v>
       </c>
       <c r="S2">
-        <v>34.40600000000001</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="T2">
-        <v>0.04404379770750024</v>
+        <v>0.1211126892252377</v>
       </c>
       <c r="U2">
-        <v>1012.96</v>
+        <v>978.175</v>
       </c>
       <c r="V2">
-        <v>0.1146372543915837</v>
+        <v>0.1027328562396419</v>
       </c>
       <c r="W2">
-        <v>0.07427937915742794</v>
+        <v>0.1109554251685787</v>
       </c>
       <c r="X2">
-        <v>0.1193248153454883</v>
+        <v>0.08838818095010835</v>
       </c>
       <c r="Y2">
-        <v>-0.04504543618806039</v>
+        <v>0.02256724421847033</v>
       </c>
       <c r="Z2">
-        <v>0.05228254690541396</v>
+        <v>0.07204788762236775</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05544028787048495</v>
+        <v>0.04764775781004016</v>
       </c>
       <c r="AC2">
-        <v>-0.05544028787048495</v>
+        <v>-0.04764775781004016</v>
       </c>
       <c r="AD2">
-        <v>33305.087</v>
+        <v>36493.95</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>33305.087</v>
+        <v>36493.95</v>
       </c>
       <c r="AG2">
-        <v>32292.127</v>
+        <v>35515.77499999999</v>
       </c>
       <c r="AH2">
-        <v>0.7903192703539071</v>
+        <v>0.7930796781692425</v>
       </c>
       <c r="AI2">
-        <v>0.7483534637754615</v>
+        <v>0.7464860757266918</v>
       </c>
       <c r="AJ2">
-        <v>0.7851549929784438</v>
+        <v>0.7885855317973551</v>
       </c>
       <c r="AK2">
-        <v>0.7424923709852725</v>
+        <v>0.7413100435769752</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0467</v>
+        <v>0.0818</v>
       </c>
       <c r="E3">
-        <v>0.0605</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>63.3</v>
+        <v>89.7</v>
       </c>
       <c r="L3">
-        <v>0.4288617886178862</v>
+        <v>0.4588235294117647</v>
       </c>
       <c r="M3">
-        <v>57.2</v>
+        <v>19.6</v>
       </c>
       <c r="N3">
-        <v>0.1353846153846154</v>
+        <v>0.04794520547945206</v>
       </c>
       <c r="O3">
-        <v>0.9036334913112165</v>
+        <v>0.2185061315496098</v>
       </c>
       <c r="P3">
-        <v>25.1</v>
+        <v>19.6</v>
       </c>
       <c r="Q3">
-        <v>0.05940828402366864</v>
+        <v>0.04794520547945206</v>
       </c>
       <c r="R3">
-        <v>0.39652448657188</v>
+        <v>0.2185061315496098</v>
       </c>
       <c r="S3">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.5611888111888111</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>62.3</v>
+        <v>15.9</v>
       </c>
       <c r="V3">
-        <v>0.1474556213017751</v>
+        <v>0.03889432485322896</v>
       </c>
       <c r="W3">
-        <v>0.07278371852362883</v>
+        <v>0.1239463866242918</v>
       </c>
       <c r="X3">
-        <v>0.1828108115698041</v>
+        <v>0.1443792770191613</v>
       </c>
       <c r="Y3">
-        <v>-0.1100270930461753</v>
+        <v>-0.02043289039486942</v>
       </c>
       <c r="Z3">
-        <v>0.0309641688344382</v>
+        <v>0.05191184280403612</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05437290700242188</v>
+        <v>0.04631326746224576</v>
       </c>
       <c r="AC3">
-        <v>-0.05437290700242188</v>
+        <v>-0.04631326746224576</v>
       </c>
       <c r="AD3">
-        <v>3104.6</v>
+        <v>3585.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3104.6</v>
+        <v>3585.9</v>
       </c>
       <c r="AG3">
-        <v>3042.3</v>
+        <v>3570</v>
       </c>
       <c r="AH3">
-        <v>0.8802132063168042</v>
+        <v>0.8976644053370716</v>
       </c>
       <c r="AI3">
-        <v>0.8109604785413891</v>
+        <v>0.8204218907293859</v>
       </c>
       <c r="AJ3">
-        <v>0.878059339644424</v>
+        <v>0.8972554539057002</v>
       </c>
       <c r="AK3">
-        <v>0.8078332448220923</v>
+        <v>0.8197662403269881</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.122</v>
+        <v>0.141</v>
       </c>
       <c r="E4">
-        <v>0.166</v>
+        <v>0.179</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>15.3</v>
+        <v>19.3</v>
       </c>
       <c r="L4">
-        <v>0.4146341463414634</v>
+        <v>0.4467592592592592</v>
       </c>
       <c r="M4">
-        <v>2.126</v>
+        <v>9.49</v>
       </c>
       <c r="N4">
-        <v>0.04392561983471074</v>
+        <v>0.1997894736842105</v>
       </c>
       <c r="O4">
-        <v>0.1389542483660131</v>
+        <v>0.4917098445595855</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="Q4">
-        <v>0.04380165289256199</v>
+        <v>0.05157894736842106</v>
       </c>
       <c r="R4">
-        <v>0.138562091503268</v>
+        <v>0.1269430051813472</v>
       </c>
       <c r="S4">
-        <v>0.005999999999999783</v>
+        <v>7.04</v>
       </c>
       <c r="T4">
-        <v>0.00282220131702718</v>
+        <v>0.7418335089567966</v>
       </c>
       <c r="U4">
-        <v>8.73</v>
+        <v>8.82</v>
       </c>
       <c r="V4">
-        <v>0.1803719008264463</v>
+        <v>0.1856842105263158</v>
       </c>
       <c r="W4">
-        <v>0.0759682224428997</v>
+        <v>0.1065121412803532</v>
       </c>
       <c r="X4">
-        <v>0.1819657076326278</v>
+        <v>0.1410278637756389</v>
       </c>
       <c r="Y4">
-        <v>-0.1059974851897281</v>
+        <v>-0.0345157224952857</v>
       </c>
       <c r="Z4">
-        <v>0.06260604004071937</v>
+        <v>0.08218083588563169</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05437774165692029</v>
+        <v>0.04633616890722238</v>
       </c>
       <c r="AC4">
-        <v>-0.05437774165692029</v>
+        <v>-0.04633616890722238</v>
       </c>
       <c r="AD4">
-        <v>353.2</v>
+        <v>401.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>353.2</v>
+        <v>401.5</v>
       </c>
       <c r="AG4">
-        <v>344.47</v>
+        <v>392.68</v>
       </c>
       <c r="AH4">
-        <v>0.8794820717131474</v>
+        <v>0.8942093541202673</v>
       </c>
       <c r="AI4">
-        <v>0.6609281437125749</v>
+        <v>0.6640754217664572</v>
       </c>
       <c r="AJ4">
-        <v>0.876804031868048</v>
+        <v>0.8920895997092099</v>
       </c>
       <c r="AK4">
-        <v>0.6552970494797116</v>
+        <v>0.6591023532176307</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandnes Sparebank (OB:SADG)</t>
+          <t>Sogn Sparebank (OB:SOGN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0416</v>
+        <v>0.201</v>
       </c>
       <c r="E5">
-        <v>0.094</v>
+        <v>0.312</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,85 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>26.8</v>
+        <v>7.95</v>
       </c>
       <c r="L5">
-        <v>0.4527027027027027</v>
+        <v>0.3859223300970874</v>
       </c>
       <c r="M5">
-        <v>21.8</v>
+        <v>4.409</v>
       </c>
       <c r="N5">
-        <v>0.1093828399397893</v>
+        <v>0.4631302521008404</v>
       </c>
       <c r="O5">
-        <v>0.8134328358208955</v>
+        <v>0.5545911949685535</v>
       </c>
       <c r="P5">
-        <v>21.8</v>
+        <v>0.659</v>
       </c>
       <c r="Q5">
-        <v>0.1093828399397893</v>
+        <v>0.06922268907563026</v>
       </c>
       <c r="R5">
-        <v>0.8134328358208955</v>
+        <v>0.08289308176100629</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.8505330006804265</v>
       </c>
       <c r="U5">
-        <v>66.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="V5">
-        <v>0.3316608128449573</v>
+        <v>8.382352941176471</v>
       </c>
       <c r="W5">
-        <v>0.07427937915742794</v>
+        <v>0.0825545171339564</v>
       </c>
       <c r="X5">
-        <v>0.1788765233656481</v>
+        <v>0.1385248969166221</v>
       </c>
       <c r="Y5">
-        <v>-0.1045971442082202</v>
+        <v>-0.05597037978266572</v>
       </c>
       <c r="Z5">
-        <v>0.03197407507426411</v>
+        <v>0.2610899873257287</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05439592782457549</v>
+        <v>0.04635430741730782</v>
       </c>
       <c r="AC5">
-        <v>-0.05439592782457549</v>
+        <v>-0.04635430741730782</v>
       </c>
       <c r="AD5">
-        <v>1417.5</v>
+        <v>78.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1417.5</v>
+        <v>78.2</v>
       </c>
       <c r="AG5">
-        <v>1351.4</v>
+        <v>-1.599999999999994</v>
       </c>
       <c r="AH5">
-        <v>0.8767318159327067</v>
+        <v>0.8914728682170543</v>
       </c>
       <c r="AI5">
-        <v>0.8249912699336515</v>
+        <v>0.4361405465699944</v>
       </c>
       <c r="AJ5">
-        <v>0.8714773973044432</v>
+        <v>-0.2020202020202012</v>
       </c>
       <c r="AK5">
-        <v>0.8179892258337873</v>
+        <v>-0.01608040201005019</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nidaros Sparebank (OB:NISB)</t>
+          <t>Sandnes Sparebank (OB:SADG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0385</v>
+        <v>0.0604</v>
       </c>
       <c r="E6">
-        <v>0.0194</v>
+        <v>0.0704</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1.99</v>
+        <v>29.1</v>
       </c>
       <c r="L6">
-        <v>0.2341176470588235</v>
+        <v>0.4279411764705883</v>
       </c>
       <c r="M6">
-        <v>0.6102</v>
+        <v>11.9</v>
       </c>
       <c r="N6">
-        <v>0.04842857142857142</v>
+        <v>0.06286318013734812</v>
       </c>
       <c r="O6">
-        <v>0.3066331658291457</v>
+        <v>0.4089347079037801</v>
       </c>
       <c r="P6">
-        <v>0.6102</v>
+        <v>11.9</v>
       </c>
       <c r="Q6">
-        <v>0.04842857142857142</v>
+        <v>0.06286318013734812</v>
       </c>
       <c r="R6">
-        <v>0.3066331658291457</v>
+        <v>0.4089347079037801</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>5.75</v>
+        <v>46.7</v>
       </c>
       <c r="V6">
-        <v>0.4563492063492063</v>
+        <v>0.2466983623877443</v>
       </c>
       <c r="W6">
-        <v>0.03251633986928104</v>
+        <v>0.09690309690309691</v>
       </c>
       <c r="X6">
-        <v>0.1677305848271244</v>
+        <v>0.1353592589236094</v>
       </c>
       <c r="Y6">
-        <v>-0.1352142449578434</v>
+        <v>-0.03845616202051245</v>
       </c>
       <c r="Z6">
-        <v>0.05141823593106327</v>
+        <v>0.04116970394139371</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05446906363349432</v>
+        <v>0.04637863755348462</v>
       </c>
       <c r="AC6">
-        <v>-0.05446906363349432</v>
+        <v>-0.04637863755348462</v>
       </c>
       <c r="AD6">
-        <v>81.2</v>
+        <v>1497.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>81.2</v>
+        <v>1497.9</v>
       </c>
       <c r="AG6">
-        <v>75.45</v>
+        <v>1451.2</v>
       </c>
       <c r="AH6">
-        <v>0.8656716417910448</v>
+        <v>0.8878022759601707</v>
       </c>
       <c r="AI6">
-        <v>0.6179604261796042</v>
+        <v>0.8217577353522054</v>
       </c>
       <c r="AJ6">
-        <v>0.8568994889267463</v>
+        <v>0.8846083511124657</v>
       </c>
       <c r="AK6">
-        <v>0.6004775169120573</v>
+        <v>0.817071110860875</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sogn Sparebank (OB:SOGN)</t>
+          <t>Totens Sparebank (OB:TOTG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="E7">
-        <v>0.212</v>
+        <v>0.09880000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,28 +1216,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5.36</v>
+        <v>27.5</v>
       </c>
       <c r="L7">
-        <v>0.3503267973856209</v>
+        <v>0.5027422303473491</v>
       </c>
       <c r="M7">
-        <v>0.506</v>
+        <v>8.08</v>
       </c>
       <c r="N7">
-        <v>0.06009501187648456</v>
+        <v>0.06495176848874598</v>
       </c>
       <c r="O7">
-        <v>0.09440298507462686</v>
+        <v>0.2938181818181818</v>
       </c>
       <c r="P7">
-        <v>0.506</v>
+        <v>8.08</v>
       </c>
       <c r="Q7">
-        <v>0.06009501187648456</v>
+        <v>0.06495176848874598</v>
       </c>
       <c r="R7">
-        <v>0.09440298507462686</v>
+        <v>0.2938181818181818</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1246,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>70.90000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="V7">
-        <v>8.420427553444181</v>
+        <v>0.06921221864951768</v>
       </c>
       <c r="W7">
-        <v>0.0485947416137806</v>
+        <v>0.1266114180478821</v>
       </c>
       <c r="X7">
-        <v>0.1662200077199834</v>
+        <v>0.1187244149994895</v>
       </c>
       <c r="Y7">
-        <v>-0.1176252661062028</v>
+        <v>0.007887003048392599</v>
       </c>
       <c r="Z7">
-        <v>0.1239870340356564</v>
+        <v>0.05414769352603445</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05447999781980395</v>
+        <v>0.04653938057248711</v>
       </c>
       <c r="AC7">
-        <v>-0.05447999781980395</v>
+        <v>-0.04653938057248711</v>
       </c>
       <c r="AD7">
-        <v>53.5</v>
+        <v>787.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>53.5</v>
+        <v>787.3</v>
       </c>
       <c r="AG7">
-        <v>-17.40000000000001</v>
+        <v>778.6899999999999</v>
       </c>
       <c r="AH7">
-        <v>0.8640180878552971</v>
+        <v>0.8635516068882307</v>
       </c>
       <c r="AI7">
-        <v>0.3571428571428571</v>
+        <v>0.761485636908792</v>
       </c>
       <c r="AJ7">
-        <v>1.937639198218262</v>
+        <v>0.8622507169828035</v>
       </c>
       <c r="AK7">
-        <v>-0.2205323193916351</v>
+        <v>0.759482682948239</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Totens Sparebank (OB:TOTG)</t>
+          <t>Melhus Sparebank (OB:MELG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0479</v>
+        <v>0.155</v>
       </c>
       <c r="E8">
-        <v>0.07530000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,28 +1338,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>21.9</v>
+        <v>13.2</v>
       </c>
       <c r="L8">
-        <v>0.4866666666666666</v>
+        <v>0.4551724137931034</v>
       </c>
       <c r="M8">
-        <v>6.94</v>
+        <v>2.86</v>
       </c>
       <c r="N8">
-        <v>0.05073099415204678</v>
+        <v>0.06485260770975056</v>
       </c>
       <c r="O8">
-        <v>0.3168949771689498</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="P8">
-        <v>6.94</v>
+        <v>2.86</v>
       </c>
       <c r="Q8">
-        <v>0.05073099415204678</v>
+        <v>0.06485260770975056</v>
       </c>
       <c r="R8">
-        <v>0.3168949771689498</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1368,55 +1368,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>24</v>
+        <v>0.315</v>
       </c>
       <c r="V8">
-        <v>0.1754385964912281</v>
+        <v>0.007142857142857143</v>
       </c>
       <c r="W8">
-        <v>0.08909682668836451</v>
+        <v>0.1144839549002602</v>
       </c>
       <c r="X8">
-        <v>0.1598507011858649</v>
+        <v>0.106365827206071</v>
       </c>
       <c r="Y8">
-        <v>-0.07075387449750035</v>
+        <v>0.008118127694189139</v>
       </c>
       <c r="Z8">
-        <v>0.03819061359585844</v>
+        <v>0.08711298554224829</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05452922407446667</v>
+        <v>0.04671239685878266</v>
       </c>
       <c r="AC8">
-        <v>-0.05452922407446667</v>
+        <v>-0.04671239685878266</v>
       </c>
       <c r="AD8">
-        <v>817</v>
+        <v>227.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>817</v>
+        <v>227.2</v>
       </c>
       <c r="AG8">
-        <v>793</v>
+        <v>226.885</v>
       </c>
       <c r="AH8">
-        <v>0.8565737051792829</v>
+        <v>0.8374493180980463</v>
       </c>
       <c r="AI8">
-        <v>0.7899825952426996</v>
+        <v>0.6293628808864266</v>
       </c>
       <c r="AJ8">
-        <v>0.8528715852871586</v>
+        <v>0.8372603649648503</v>
       </c>
       <c r="AK8">
-        <v>0.7849930706790734</v>
+        <v>0.629039189320321</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SpareBank 1 Nordmøre (OB:SNOR)</t>
+          <t>SpareBank 1 SR-Bank ASA (OB:SRBNK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.103</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E9">
-        <v>0.0629</v>
+        <v>0.113</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1460,85 +1460,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>21.5</v>
+        <v>372.5</v>
       </c>
       <c r="L9">
-        <v>0.3041018387553041</v>
+        <v>0.4841434884325448</v>
       </c>
       <c r="M9">
-        <v>5.47</v>
+        <v>195.6</v>
       </c>
       <c r="N9">
-        <v>0.04756521739130434</v>
+        <v>0.05825416207523007</v>
       </c>
       <c r="O9">
-        <v>0.2544186046511628</v>
+        <v>0.5251006711409396</v>
       </c>
       <c r="P9">
-        <v>5.47</v>
+        <v>182</v>
       </c>
       <c r="Q9">
-        <v>0.04756521739130434</v>
+        <v>0.05420377043809751</v>
       </c>
       <c r="R9">
-        <v>0.2544186046511628</v>
+        <v>0.4885906040268456</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>13.59999999999999</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.06952965235173822</v>
       </c>
       <c r="U9">
-        <v>105</v>
+        <v>39.3</v>
       </c>
       <c r="V9">
-        <v>0.9130434782608695</v>
+        <v>0.01170444053965512</v>
       </c>
       <c r="W9">
-        <v>0.05683320116309807</v>
+        <v>0.1444806454115274</v>
       </c>
       <c r="X9">
-        <v>0.1505343006495951</v>
+        <v>0.104588351429466</v>
       </c>
       <c r="Y9">
-        <v>-0.09370109948649707</v>
+        <v>0.03989229398206146</v>
       </c>
       <c r="Z9">
-        <v>0.07801551482515476</v>
+        <v>0.04470292945373415</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05461178006331811</v>
+        <v>0.04674287992118269</v>
       </c>
       <c r="AC9">
-        <v>-0.05461178006331811</v>
+        <v>-0.04674287992118269</v>
       </c>
       <c r="AD9">
-        <v>622.6</v>
+        <v>16730.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>622.6</v>
+        <v>16730.3</v>
       </c>
       <c r="AG9">
-        <v>517.6</v>
+        <v>16691</v>
       </c>
       <c r="AH9">
-        <v>0.8440889370932755</v>
+        <v>0.8328504579848666</v>
       </c>
       <c r="AI9">
-        <v>0.641921847613156</v>
+        <v>0.8516704761226017</v>
       </c>
       <c r="AJ9">
-        <v>0.8182105595953209</v>
+        <v>0.8325228069650401</v>
       </c>
       <c r="AK9">
-        <v>0.5984506879408024</v>
+        <v>0.8513731331102588</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SpareBank 1 SR-Bank ASA (OB:SRBNK)</t>
+          <t>Sparebank 68° Nord (OB:SB68)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.08539999999999999</v>
+        <v>0.224</v>
       </c>
       <c r="E10">
-        <v>0.108</v>
+        <v>0.233</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1582,28 +1582,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>300.8</v>
+        <v>11.9</v>
       </c>
       <c r="L10">
-        <v>0.4743731272669926</v>
+        <v>0.4391143911439114</v>
       </c>
       <c r="M10">
-        <v>221.6</v>
+        <v>2.64627</v>
       </c>
       <c r="N10">
-        <v>0.07073318650451658</v>
+        <v>0.05478819875776399</v>
       </c>
       <c r="O10">
-        <v>0.7367021276595744</v>
+        <v>0.2223756302521009</v>
       </c>
       <c r="P10">
-        <v>221.6</v>
+        <v>2.64627</v>
       </c>
       <c r="Q10">
-        <v>0.07073318650451658</v>
+        <v>0.05478819875776399</v>
       </c>
       <c r="R10">
-        <v>0.7367021276595744</v>
+        <v>0.2223756302521009</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1612,55 +1612,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>121.6</v>
+        <v>6.85</v>
       </c>
       <c r="V10">
-        <v>0.03881387851511379</v>
+        <v>0.1418219461697723</v>
       </c>
       <c r="W10">
-        <v>0.09959275568652121</v>
+        <v>0.09612277867528272</v>
       </c>
       <c r="X10">
-        <v>0.1387820625362035</v>
+        <v>0.09735633878403041</v>
       </c>
       <c r="Y10">
-        <v>-0.0391893068496823</v>
+        <v>-0.001233560108747686</v>
       </c>
       <c r="Z10">
-        <v>0.03479439426696371</v>
+        <v>0.08530596826995719</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05473894994435685</v>
+        <v>0.04688700570695607</v>
       </c>
       <c r="AC10">
-        <v>-0.05473894994435685</v>
+        <v>-0.04688700570695607</v>
       </c>
       <c r="AD10">
-        <v>14754.8</v>
+        <v>207.4</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>14754.8</v>
+        <v>207.4</v>
       </c>
       <c r="AG10">
-        <v>14633.2</v>
+        <v>200.55</v>
       </c>
       <c r="AH10">
-        <v>0.8248573041810853</v>
+        <v>0.811106765741103</v>
       </c>
       <c r="AI10">
-        <v>0.8512548318236889</v>
+        <v>0.6066101199181048</v>
       </c>
       <c r="AJ10">
-        <v>0.8236585407039249</v>
+        <v>0.8059071729957805</v>
       </c>
       <c r="AK10">
-        <v>0.8502039346014851</v>
+        <v>0.5985673780032831</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sparebank 68° Nord (OB:SB68)</t>
+          <t>Aurskog Sparebank (OB:AURG)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.252</v>
+        <v>0.146</v>
       </c>
       <c r="E11">
-        <v>0.267</v>
+        <v>0.189</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1704,28 +1704,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>10.2</v>
+        <v>20.1</v>
       </c>
       <c r="L11">
-        <v>0.3908045977011494</v>
+        <v>0.4975247524752476</v>
       </c>
       <c r="M11">
-        <v>2.18889</v>
+        <v>4.33</v>
       </c>
       <c r="N11">
-        <v>0.04225656370656371</v>
+        <v>0.04278656126482214</v>
       </c>
       <c r="O11">
-        <v>0.2145970588235294</v>
+        <v>0.2154228855721393</v>
       </c>
       <c r="P11">
-        <v>2.18889</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>0.04225656370656371</v>
+        <v>0.04278656126482214</v>
       </c>
       <c r="R11">
-        <v>0.2145970588235294</v>
+        <v>0.2154228855721393</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1734,55 +1734,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>7.02</v>
+        <v>59.6</v>
       </c>
       <c r="V11">
-        <v>0.1355212355212355</v>
+        <v>0.5889328063241107</v>
       </c>
       <c r="W11">
-        <v>0.07088255733148019</v>
+        <v>0.1197141155449672</v>
       </c>
       <c r="X11">
-        <v>0.1249111217336028</v>
+        <v>0.09449726014952509</v>
       </c>
       <c r="Y11">
-        <v>-0.05402856440212259</v>
+        <v>0.02521685539544216</v>
       </c>
       <c r="Z11">
-        <v>0.06867336736304794</v>
+        <v>0.08697524219590957</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05493629088168034</v>
+        <v>0.0469548868696024</v>
       </c>
       <c r="AC11">
-        <v>-0.05493629088168034</v>
+        <v>-0.0469548868696024</v>
       </c>
       <c r="AD11">
-        <v>200.9</v>
+        <v>407</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>200.9</v>
+        <v>407</v>
       </c>
       <c r="AG11">
-        <v>193.88</v>
+        <v>347.4</v>
       </c>
       <c r="AH11">
-        <v>0.7950138504155125</v>
+        <v>0.8008658008658008</v>
       </c>
       <c r="AI11">
-        <v>0.6187249769017555</v>
+        <v>0.6835740678535439</v>
       </c>
       <c r="AJ11">
-        <v>0.789156626506024</v>
+        <v>0.7744092732946947</v>
       </c>
       <c r="AK11">
-        <v>0.6102996726265424</v>
+        <v>0.6483762597984323</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aurskog Sparebank (OB:AURG)</t>
+          <t>Aasen Sparebank (OB:AASB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.09759999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="E12">
-        <v>0.113</v>
+        <v>0.186</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1826,28 +1826,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>13.7</v>
+        <v>7.39</v>
       </c>
       <c r="L12">
-        <v>0.4581939799331103</v>
+        <v>0.4767741935483871</v>
       </c>
       <c r="M12">
-        <v>4.59</v>
+        <v>1.0553</v>
       </c>
       <c r="N12">
-        <v>0.04447674418604651</v>
+        <v>0.04690222222222222</v>
       </c>
       <c r="O12">
-        <v>0.335036496350365</v>
+        <v>0.1428010825439783</v>
       </c>
       <c r="P12">
-        <v>4.59</v>
+        <v>1.0553</v>
       </c>
       <c r="Q12">
-        <v>0.04447674418604651</v>
+        <v>0.04690222222222222</v>
       </c>
       <c r="R12">
-        <v>0.335036496350365</v>
+        <v>0.1428010825439783</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1856,55 +1856,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>69.09999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="V12">
-        <v>0.6695736434108527</v>
+        <v>0.5911111111111111</v>
       </c>
       <c r="W12">
-        <v>0.07974388824214201</v>
+        <v>0.1353479853479853</v>
       </c>
       <c r="X12">
-        <v>0.1193248153454883</v>
+        <v>0.08838818095010835</v>
       </c>
       <c r="Y12">
-        <v>-0.03958092710334632</v>
+        <v>0.04695980439787699</v>
       </c>
       <c r="Z12">
-        <v>0.05829596412556053</v>
+        <v>0.107177430507537</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.05503616281436212</v>
+        <v>0.04712782850227665</v>
       </c>
       <c r="AC12">
-        <v>-0.05503616281436212</v>
+        <v>-0.04712782850227665</v>
       </c>
       <c r="AD12">
-        <v>365.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>365.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AG12">
-        <v>296.6</v>
+        <v>64.10000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.7799104286628279</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="AI12">
-        <v>0.6853448275862069</v>
+        <v>0.5315934065934066</v>
       </c>
       <c r="AJ12">
-        <v>0.7418709354677339</v>
+        <v>0.7401847575057737</v>
       </c>
       <c r="AK12">
-        <v>0.6385360602798709</v>
+        <v>0.4845049130763417</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SpareBank 1 SMN (OB:MING)</t>
+          <t>Sunndal Sparebank (OB:SUNSB)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0733</v>
+        <v>0.157</v>
       </c>
       <c r="E13">
-        <v>0.0824</v>
+        <v>0.187</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1948,85 +1948,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>237.7</v>
+        <v>5.65</v>
       </c>
       <c r="L13">
-        <v>0.408068669527897</v>
+        <v>0.3575949367088608</v>
       </c>
       <c r="M13">
-        <v>133.14</v>
+        <v>2.50608</v>
       </c>
       <c r="N13">
-        <v>0.0796339493988875</v>
+        <v>0.08084129032258064</v>
       </c>
       <c r="O13">
-        <v>0.5601177955405975</v>
+        <v>0.4435539823008849</v>
       </c>
       <c r="P13">
-        <v>131.3</v>
+        <v>2.50608</v>
       </c>
       <c r="Q13">
-        <v>0.078533405107961</v>
+        <v>0.08084129032258064</v>
       </c>
       <c r="R13">
-        <v>0.5523769457299117</v>
+        <v>0.4435539823008849</v>
       </c>
       <c r="S13">
-        <v>1.840000000000003</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.01382003905663214</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>29.2</v>
+        <v>7.44</v>
       </c>
       <c r="V13">
-        <v>0.01746515939948561</v>
+        <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.09329617709396341</v>
+        <v>0.07318652849740932</v>
       </c>
       <c r="X13">
-        <v>0.1131052861781472</v>
+        <v>0.08705348603460822</v>
       </c>
       <c r="Y13">
-        <v>-0.01980910908418382</v>
+        <v>-0.0138669575371989</v>
       </c>
       <c r="Z13">
-        <v>0.07096648432645802</v>
+        <v>0.09288653733098179</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05516621679280174</v>
+        <v>0.04717182217705949</v>
       </c>
       <c r="AC13">
-        <v>-0.05516621679280174</v>
+        <v>-0.04717182217705949</v>
       </c>
       <c r="AD13">
-        <v>5301.4</v>
+        <v>102.7</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>5301.4</v>
+        <v>102.7</v>
       </c>
       <c r="AG13">
-        <v>5272.2</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="AH13">
-        <v>0.760242639783173</v>
+        <v>0.768137621540763</v>
       </c>
       <c r="AI13">
-        <v>0.7069947322797893</v>
+        <v>0.5721448467966574</v>
       </c>
       <c r="AJ13">
-        <v>0.7592344580291182</v>
+        <v>0.754474893077776</v>
       </c>
       <c r="AK13">
-        <v>0.7058492763712798</v>
+        <v>0.5536440776473324</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jæren Sparebank (OB:JAREN)</t>
+          <t>SpareBank 1 SMN (OB:MING)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0507</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="E14">
-        <v>0.0554</v>
+        <v>0.0706</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2070,85 +2070,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>17.2</v>
+        <v>290.2</v>
       </c>
       <c r="L14">
-        <v>0.4751381215469613</v>
+        <v>0.4513219284603421</v>
       </c>
       <c r="M14">
-        <v>9.550000000000001</v>
+        <v>136.4</v>
       </c>
       <c r="N14">
-        <v>0.08031959629941127</v>
+        <v>0.06782357913579634</v>
       </c>
       <c r="O14">
-        <v>0.555232558139535</v>
+        <v>0.4700206753962785</v>
       </c>
       <c r="P14">
-        <v>9.550000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="Q14">
-        <v>0.08031959629941127</v>
+        <v>0.04400576798766844</v>
       </c>
       <c r="R14">
-        <v>0.555232558139535</v>
+        <v>0.3049620951068229</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>47.90000000000001</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>0.3511730205278593</v>
       </c>
       <c r="U14">
-        <v>8.029999999999999</v>
+        <v>111.3</v>
       </c>
       <c r="V14">
-        <v>0.06753574432296046</v>
+        <v>0.05534284719805082</v>
       </c>
       <c r="W14">
-        <v>0.07248209018120522</v>
+        <v>0.1373402744912447</v>
       </c>
       <c r="X14">
-        <v>0.10560842492993</v>
+        <v>0.08203551655584129</v>
       </c>
       <c r="Y14">
-        <v>-0.0331263347487248</v>
+        <v>0.05530475793540338</v>
       </c>
       <c r="Z14">
-        <v>0.05833158768268904</v>
+        <v>0.08706602393977143</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05535760480038119</v>
+        <v>0.04736331233024135</v>
       </c>
       <c r="AC14">
-        <v>-0.05535760480038119</v>
+        <v>-0.04736331233024135</v>
       </c>
       <c r="AD14">
-        <v>323.6</v>
+        <v>5701.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>323.6</v>
+        <v>5701.6</v>
       </c>
       <c r="AG14">
-        <v>315.5700000000001</v>
+        <v>5590.3</v>
       </c>
       <c r="AH14">
-        <v>0.7312994350282487</v>
+        <v>0.7392482528816108</v>
       </c>
       <c r="AI14">
-        <v>0.6119515885022694</v>
+        <v>0.6888070069465418</v>
       </c>
       <c r="AJ14">
-        <v>0.7263332335949548</v>
+        <v>0.7354303154682033</v>
       </c>
       <c r="AK14">
-        <v>0.6059680857192236</v>
+        <v>0.6845656486493106</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SpareBank 1 Helgeland (OB:HELG)</t>
+          <t>Jæren Sparebank (OB:JAREN)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0555</v>
+        <v>0.091</v>
       </c>
       <c r="E15">
-        <v>0.008369999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2192,28 +2192,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>27.1</v>
+        <v>21.4</v>
       </c>
       <c r="L15">
-        <v>0.3533246414602347</v>
+        <v>0.4724061810154526</v>
       </c>
       <c r="M15">
-        <v>9.94</v>
+        <v>11.1</v>
       </c>
       <c r="N15">
-        <v>0.03024034073623365</v>
+        <v>0.08644859813084112</v>
       </c>
       <c r="O15">
-        <v>0.3667896678966789</v>
+        <v>0.5186915887850467</v>
       </c>
       <c r="P15">
-        <v>9.94</v>
+        <v>11.1</v>
       </c>
       <c r="Q15">
-        <v>0.03024034073623365</v>
+        <v>0.08644859813084112</v>
       </c>
       <c r="R15">
-        <v>0.3667896678966789</v>
+        <v>0.5186915887850467</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2222,55 +2222,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>81.09999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="V15">
-        <v>0.2467295406145421</v>
+        <v>0.02468847352024922</v>
       </c>
       <c r="W15">
-        <v>0.0560264626834815</v>
+        <v>0.1042884990253411</v>
       </c>
       <c r="X15">
-        <v>0.1028470145780647</v>
+        <v>0.07931018922440497</v>
       </c>
       <c r="Y15">
-        <v>-0.04682055189458317</v>
+        <v>0.02497830980093615</v>
       </c>
       <c r="Z15">
-        <v>0.04766343524732786</v>
+        <v>0.08698657756783225</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.05544028787048495</v>
+        <v>0.04748876056286996</v>
       </c>
       <c r="AC15">
-        <v>-0.05544028787048495</v>
+        <v>-0.04748876056286996</v>
       </c>
       <c r="AD15">
-        <v>840.2</v>
+        <v>330.7</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>840.2</v>
+        <v>330.7</v>
       </c>
       <c r="AG15">
-        <v>759.1</v>
+        <v>327.53</v>
       </c>
       <c r="AH15">
-        <v>0.7187954487124647</v>
+        <v>0.7203223698540623</v>
       </c>
       <c r="AI15">
-        <v>0.6566114410753361</v>
+        <v>0.5936097648537066</v>
       </c>
       <c r="AJ15">
-        <v>0.6978304835447693</v>
+        <v>0.7183778211567565</v>
       </c>
       <c r="AK15">
-        <v>0.633375052148519</v>
+        <v>0.591284097268608</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SpareBank 1 Sørøst-Norge (OB:SOON)</t>
+          <t>Grong Sparebank (OB:GRONG)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.151</v>
+        <v>0.145</v>
       </c>
       <c r="E16">
-        <v>0.167</v>
+        <v>0.254</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2314,28 +2314,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>84.7</v>
+        <v>14.4</v>
       </c>
       <c r="L16">
-        <v>0.4178589047853972</v>
+        <v>0.4784053156146179</v>
       </c>
       <c r="M16">
-        <v>45.7</v>
+        <v>3.3348</v>
       </c>
       <c r="N16">
-        <v>0.0584473717866735</v>
+        <v>0.05749655172413793</v>
       </c>
       <c r="O16">
-        <v>0.539551357733176</v>
+        <v>0.2315833333333333</v>
       </c>
       <c r="P16">
-        <v>45.7</v>
+        <v>3.3348</v>
       </c>
       <c r="Q16">
-        <v>0.0584473717866735</v>
+        <v>0.05749655172413793</v>
       </c>
       <c r="R16">
-        <v>0.539551357733176</v>
+        <v>0.2315833333333333</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2344,55 +2344,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>111.7</v>
+        <v>7.06</v>
       </c>
       <c r="V16">
-        <v>0.1428571428571429</v>
+        <v>0.1217241379310345</v>
       </c>
       <c r="W16">
-        <v>0.07475068396434562</v>
+        <v>0.1322314049586777</v>
       </c>
       <c r="X16">
-        <v>0.09995017602198857</v>
+        <v>0.07634415382271846</v>
       </c>
       <c r="Y16">
-        <v>-0.02519949205764295</v>
+        <v>0.05588725113595923</v>
       </c>
       <c r="Z16">
-        <v>0.07011414735385679</v>
+        <v>0.1219067676481309</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.05553572112507292</v>
+        <v>0.04764775781004016</v>
       </c>
       <c r="AC16">
-        <v>-0.05553572112507292</v>
+        <v>-0.04764775781004016</v>
       </c>
       <c r="AD16">
-        <v>1862.9</v>
+        <v>133</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1862.9</v>
+        <v>133</v>
       </c>
       <c r="AG16">
-        <v>1751.2</v>
+        <v>125.94</v>
       </c>
       <c r="AH16">
-        <v>0.7043632788868723</v>
+        <v>0.6963350785340314</v>
       </c>
       <c r="AI16">
-        <v>0.6198096885813148</v>
+        <v>0.5450819672131147</v>
       </c>
       <c r="AJ16">
-        <v>0.6913268327345941</v>
+        <v>0.6846797868870284</v>
       </c>
       <c r="AK16">
-        <v>0.605134939009641</v>
+        <v>0.5315269688528741</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SpareBank 1 Nord-Norge (OB:NONG)</t>
+          <t>SpareBank 1 Sørøst-Norge (OB:SOON)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0675</v>
+        <v>0.198</v>
       </c>
       <c r="E17">
-        <v>0.0788</v>
+        <v>0.169</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2436,28 +2436,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>172.7</v>
+        <v>126.7</v>
       </c>
       <c r="L17">
-        <v>0.4560337998415632</v>
+        <v>0.4428521495980426</v>
       </c>
       <c r="M17">
-        <v>224</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N17">
-        <v>0.2289686190330165</v>
+        <v>0.1005769883470981</v>
       </c>
       <c r="O17">
-        <v>1.297046902142444</v>
+        <v>0.7016574585635359</v>
       </c>
       <c r="P17">
-        <v>224</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q17">
-        <v>0.2289686190330165</v>
+        <v>0.1005769883470981</v>
       </c>
       <c r="R17">
-        <v>1.297046902142444</v>
+        <v>0.7016574585635359</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2466,55 +2466,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>11</v>
+        <v>228.4</v>
       </c>
       <c r="V17">
-        <v>0.01124399468465706</v>
+        <v>0.2584002715239281</v>
       </c>
       <c r="W17">
-        <v>0.09078006728343145</v>
+        <v>0.1109554251685787</v>
       </c>
       <c r="X17">
-        <v>0.09546882380932897</v>
+        <v>0.07580388635293256</v>
       </c>
       <c r="Y17">
-        <v>-0.004688756525897522</v>
+        <v>0.03515153881564612</v>
       </c>
       <c r="Z17">
-        <v>0.0819732455950474</v>
+        <v>0.1002382453927545</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.05570431713913686</v>
+        <v>0.0476797024058064</v>
       </c>
       <c r="AC17">
-        <v>-0.05570431713913686</v>
+        <v>-0.0476797024058064</v>
       </c>
       <c r="AD17">
-        <v>2068.1</v>
+        <v>1981.4</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>2068.1</v>
+        <v>1981.4</v>
       </c>
       <c r="AG17">
-        <v>2057.1</v>
+        <v>1753</v>
       </c>
       <c r="AH17">
-        <v>0.6788668592436975</v>
+        <v>0.6915157226119429</v>
       </c>
       <c r="AI17">
-        <v>0.5882135441849883</v>
+        <v>0.6232189475670745</v>
       </c>
       <c r="AJ17">
-        <v>0.6777031033801147</v>
+        <v>0.6647957829269218</v>
       </c>
       <c r="AK17">
-        <v>0.5869211675083454</v>
+        <v>0.5940560506963977</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grong Sparebank (OB:GRONG)</t>
+          <t>SpareBank 1 Nord-Norge (OB:NONG)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2539,6 +2539,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.0775</v>
+      </c>
+      <c r="E18">
+        <v>0.0877</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2552,28 +2558,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>12.8</v>
+        <v>227.7</v>
       </c>
       <c r="L18">
-        <v>0.5059288537549407</v>
+        <v>0.4897827489782749</v>
       </c>
       <c r="M18">
-        <v>3.29113</v>
+        <v>57.9</v>
       </c>
       <c r="N18">
-        <v>0.05134368174726989</v>
+        <v>0.05666470933646506</v>
       </c>
       <c r="O18">
-        <v>0.25711953125</v>
+        <v>0.2542819499341238</v>
       </c>
       <c r="P18">
-        <v>3.29113</v>
+        <v>57.9</v>
       </c>
       <c r="Q18">
-        <v>0.05134368174726989</v>
+        <v>0.05666470933646506</v>
       </c>
       <c r="R18">
-        <v>0.25711953125</v>
+        <v>0.2542819499341238</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2582,55 +2588,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>6.95</v>
+        <v>11.8</v>
       </c>
       <c r="V18">
-        <v>0.1084243369734789</v>
+        <v>0.01154824818946957</v>
       </c>
       <c r="W18">
-        <v>0.122488038277512</v>
+        <v>0.1591973711808712</v>
       </c>
       <c r="X18">
-        <v>0.09262980521377664</v>
+        <v>0.07453746477047253</v>
       </c>
       <c r="Y18">
-        <v>0.02985823306373532</v>
+        <v>0.08465990641039862</v>
       </c>
       <c r="Z18">
-        <v>0.09148866155342686</v>
+        <v>0.1333084819636405</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.05582704247060458</v>
+        <v>0.04775871021431402</v>
       </c>
       <c r="AC18">
-        <v>-0.05582704247060458</v>
+        <v>-0.04775871021431402</v>
       </c>
       <c r="AD18">
-        <v>124.6</v>
+        <v>2167.3</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>124.6</v>
+        <v>2167.3</v>
       </c>
       <c r="AG18">
-        <v>117.65</v>
+        <v>2155.5</v>
       </c>
       <c r="AH18">
-        <v>0.6603073661897192</v>
+        <v>0.6795961242983913</v>
       </c>
       <c r="AI18">
-        <v>0.5498676081200353</v>
+        <v>0.5892444468611512</v>
       </c>
       <c r="AJ18">
-        <v>0.6473177441540577</v>
+        <v>0.6784061939382494</v>
       </c>
       <c r="AK18">
-        <v>0.535624857728204</v>
+        <v>0.587922428606497</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2656,10 +2662,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0815</v>
+        <v>0.101</v>
       </c>
       <c r="E19">
-        <v>0.215</v>
+        <v>0.12</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2674,85 +2680,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>4.52</v>
+        <v>6.41</v>
       </c>
       <c r="L19">
-        <v>0.4224299065420561</v>
+        <v>0.4162337662337662</v>
       </c>
       <c r="M19">
-        <v>2.02</v>
+        <v>6.109999999999999</v>
       </c>
       <c r="N19">
-        <v>0.04064386317907445</v>
+        <v>0.1163809523809524</v>
       </c>
       <c r="O19">
-        <v>0.4469026548672567</v>
+        <v>0.9531981279251169</v>
       </c>
       <c r="P19">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="Q19">
-        <v>0.04064386317907445</v>
+        <v>0.04495238095238095</v>
       </c>
       <c r="R19">
-        <v>0.4469026548672567</v>
+        <v>0.3681747269890795</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.613747954173486</v>
       </c>
       <c r="U19">
-        <v>18.5</v>
+        <v>26.6</v>
       </c>
       <c r="V19">
-        <v>0.3722334004024145</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="W19">
-        <v>0.06484935437589669</v>
+        <v>0.1091993185689949</v>
       </c>
       <c r="X19">
-        <v>0.0923918464508733</v>
+        <v>0.07326615530850276</v>
       </c>
       <c r="Y19">
-        <v>-0.02754249207497661</v>
+        <v>0.03593316326049212</v>
       </c>
       <c r="Z19">
-        <v>0.06353919239904987</v>
+        <v>0.1131520940484937</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.05583797643275003</v>
+        <v>0.04784441176950092</v>
       </c>
       <c r="AC19">
-        <v>-0.05583797643275003</v>
+        <v>-0.04784441176950092</v>
       </c>
       <c r="AD19">
-        <v>95.90000000000001</v>
+        <v>105</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>95.90000000000001</v>
+        <v>105</v>
       </c>
       <c r="AG19">
-        <v>77.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AH19">
-        <v>0.6586538461538461</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI19">
-        <v>0.6203104786545924</v>
+        <v>0.6180105944673338</v>
       </c>
       <c r="AJ19">
-        <v>0.6089693154996066</v>
+        <v>0.5989304812834225</v>
       </c>
       <c r="AK19">
-        <v>0.5686994856722998</v>
+        <v>0.5471039776692254</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2769,7 +2775,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SpareBank 1 Østfold Akershus (OB:SOAG)</t>
+          <t>SpareBank 1 Helgeland (OB:HELG)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2778,10 +2784,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0573</v>
+        <v>0.146</v>
       </c>
       <c r="E20">
-        <v>0.0505</v>
+        <v>0.191</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2796,85 +2802,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>35.8</v>
+        <v>52</v>
       </c>
       <c r="L20">
-        <v>0.4323671497584541</v>
+        <v>0.4990403071017274</v>
       </c>
       <c r="M20">
-        <v>24.46</v>
+        <v>30.9</v>
       </c>
       <c r="N20">
-        <v>0.06158106747230615</v>
+        <v>0.08938385883714203</v>
       </c>
       <c r="O20">
-        <v>0.6832402234636872</v>
+        <v>0.5942307692307692</v>
       </c>
       <c r="P20">
-        <v>24</v>
+        <v>30.9</v>
       </c>
       <c r="Q20">
-        <v>0.06042296072507553</v>
+        <v>0.08938385883714203</v>
       </c>
       <c r="R20">
-        <v>0.670391061452514</v>
+        <v>0.5942307692307692</v>
       </c>
       <c r="S20">
-        <v>0.4600000000000009</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>0.01880621422730993</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>141</v>
+        <v>112.2</v>
       </c>
       <c r="V20">
-        <v>0.3549848942598187</v>
+        <v>0.3245588660688458</v>
       </c>
       <c r="W20">
-        <v>0.07755632582322355</v>
+        <v>0.1183970856102004</v>
       </c>
       <c r="X20">
-        <v>0.07433848958645622</v>
+        <v>0.07190525562681037</v>
       </c>
       <c r="Y20">
-        <v>0.00321783623676733</v>
+        <v>0.04649182998338999</v>
       </c>
       <c r="Z20">
-        <v>0.1063174114021572</v>
+        <v>0.08695652173913042</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.05715963736713505</v>
+        <v>0.047944163896189</v>
       </c>
       <c r="AC20">
-        <v>-0.05715963736713505</v>
+        <v>-0.047944163896189</v>
       </c>
       <c r="AD20">
-        <v>336.7</v>
+        <v>646.6</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>336.7</v>
+        <v>646.6</v>
       </c>
       <c r="AG20">
-        <v>195.7</v>
+        <v>534.4</v>
       </c>
       <c r="AH20">
-        <v>0.4587818503883363</v>
+        <v>0.6516174543988713</v>
       </c>
       <c r="AI20">
-        <v>0.468941504178273</v>
+        <v>0.5812657317511686</v>
       </c>
       <c r="AJ20">
-        <v>0.3300725248777197</v>
+        <v>0.6072037268492217</v>
       </c>
       <c r="AK20">
-        <v>0.3391681109185442</v>
+        <v>0.5342931413717256</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2891,7 +2897,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kraft Bank ASA (OB:KRAB)</t>
+          <t>Bien Sparebank ASA (OB:BIEN)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2899,6 +2905,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D21">
+        <v>0.101</v>
+      </c>
+      <c r="E21">
+        <v>0.135</v>
+      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2912,28 +2924,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>4.38</v>
+        <v>5.14</v>
       </c>
       <c r="L21">
-        <v>0.3395348837209302</v>
+        <v>0.3807407407407407</v>
       </c>
       <c r="M21">
-        <v>0.967</v>
+        <v>1.97</v>
       </c>
       <c r="N21">
-        <v>0.0256498673740053</v>
+        <v>0.04053497942386831</v>
       </c>
       <c r="O21">
-        <v>0.2207762557077625</v>
+        <v>0.3832684824902724</v>
       </c>
       <c r="P21">
-        <v>0.967</v>
+        <v>1.97</v>
       </c>
       <c r="Q21">
-        <v>0.0256498673740053</v>
+        <v>0.04053497942386831</v>
       </c>
       <c r="R21">
-        <v>0.2207762557077625</v>
+        <v>0.3832684824902724</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2942,55 +2954,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>7.13</v>
+        <v>12</v>
       </c>
       <c r="V21">
-        <v>0.1891246684350132</v>
+        <v>0.2469135802469136</v>
       </c>
       <c r="W21">
-        <v>0.1081481481481481</v>
+        <v>0.09771863117870722</v>
       </c>
       <c r="X21">
-        <v>0.06033808632550555</v>
+        <v>0.06890137310170646</v>
       </c>
       <c r="Y21">
-        <v>0.04781006182264259</v>
+        <v>0.02881725807700075</v>
       </c>
       <c r="Z21">
-        <v>0.3460578909246989</v>
+        <v>0.112942357567138</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.06013648703477948</v>
+        <v>0.04819975567470489</v>
       </c>
       <c r="AC21">
-        <v>-0.06013648703477948</v>
+        <v>-0.04819975567470489</v>
       </c>
       <c r="AD21">
-        <v>0.327</v>
+        <v>77</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0.327</v>
+        <v>77</v>
       </c>
       <c r="AG21">
-        <v>-6.803</v>
+        <v>65</v>
       </c>
       <c r="AH21">
-        <v>0.008599153233229021</v>
+        <v>0.6130573248407644</v>
       </c>
       <c r="AI21">
-        <v>0.009026416760979381</v>
+        <v>0.55</v>
       </c>
       <c r="AJ21">
-        <v>-0.2201831893064051</v>
+        <v>0.5721830985915494</v>
       </c>
       <c r="AK21">
-        <v>-0.2338041722514349</v>
+        <v>0.5078125</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3007,7 +3019,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Instabank ASA (OB:INSTA)</t>
+          <t>SpareBank 1 Østfold Akershus (OB:SOAG)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3016,7 +3028,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.351</v>
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="E22">
+        <v>0.0766</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3031,82 +3046,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>7.58</v>
+        <v>50.5</v>
       </c>
       <c r="L22">
-        <v>0.319831223628692</v>
+        <v>0.466728280961183</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>22.1</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.05695876288659794</v>
       </c>
       <c r="O22">
-        <v>-0</v>
+        <v>0.4376237623762377</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>22.1</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.05695876288659794</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>0.4376237623762377</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
       <c r="U22">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>0.2912371134020619</v>
       </c>
       <c r="W22">
-        <v>0.1031292517006803</v>
+        <v>0.1324416469971151</v>
       </c>
       <c r="X22">
-        <v>0.06175367456918252</v>
+        <v>0.06297315281798407</v>
       </c>
       <c r="Y22">
-        <v>0.04137557713149775</v>
+        <v>0.06946849417913106</v>
       </c>
       <c r="Z22">
-        <v>0.2937530986613783</v>
+        <v>0.1875216637781629</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.06014148386967998</v>
+        <v>0.04891658169118007</v>
       </c>
       <c r="AC22">
-        <v>-0.06014148386967998</v>
+        <v>-0.04891658169118007</v>
       </c>
       <c r="AD22">
-        <v>5.76</v>
+        <v>395.7</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>5.76</v>
+        <v>395.7</v>
       </c>
       <c r="AG22">
-        <v>5.76</v>
+        <v>282.7</v>
       </c>
       <c r="AH22">
-        <v>0.08551068883610451</v>
+        <v>0.504912594104887</v>
       </c>
       <c r="AI22">
-        <v>0.0797121505673955</v>
+        <v>0.489061920652577</v>
       </c>
       <c r="AJ22">
-        <v>0.08551068883610451</v>
+        <v>0.4214999254510213</v>
       </c>
       <c r="AK22">
-        <v>0.0797121505673955</v>
+        <v>0.406119810372073</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3123,7 +3141,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aprila Bank ASA (OTCNO:APRILA)</t>
+          <t>Kraft Bank ASA (OB:KRAB)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3144,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>-1.26</v>
+        <v>4.66</v>
       </c>
       <c r="L23">
-        <v>-0.2703862660944206</v>
+        <v>0.3530303030303031</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3156,7 +3174,7 @@
         <v>-0</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3165,61 +3183,61 @@
         <v>-0</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>0.09023136246786632</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="W23">
-        <v>-0.1305699481865285</v>
+        <v>0.1213541666666667</v>
       </c>
       <c r="X23">
-        <v>0.06019334925228834</v>
+        <v>0.05347945309505931</v>
       </c>
       <c r="Y23">
-        <v>-0.1907632974388168</v>
+        <v>0.06787471357160738</v>
       </c>
       <c r="Z23">
-        <v>1.033259423503326</v>
+        <v>0.3898635477582845</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.06019334925228834</v>
+        <v>0.05157540906278815</v>
       </c>
       <c r="AC23">
-        <v>-0.06019334925228834</v>
+        <v>-0.05157540906278815</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AG23">
-        <v>-3.51</v>
+        <v>-1.97</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>0.1037857326809168</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>0.09132109675957399</v>
       </c>
       <c r="AJ23">
-        <v>-0.09918055948007912</v>
+        <v>-0.06000609198903441</v>
       </c>
       <c r="AK23">
-        <v>-0.3054830287206266</v>
+        <v>-0.05166535536323104</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3236,7 +3254,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tysnes Sparebank (OB:TYSB)</t>
+          <t>Høland og Setskog Sparebank (OB:HSPG)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3245,10 +3263,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.09420000000000001</v>
+        <v>0.0224</v>
       </c>
       <c r="E24">
-        <v>0.143</v>
+        <v>-0.0309</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3263,28 +3281,28 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>2.83</v>
+        <v>4.46</v>
       </c>
       <c r="L24">
-        <v>0.3793565683646113</v>
+        <v>0.3097222222222222</v>
       </c>
       <c r="M24">
-        <v>1.2533</v>
+        <v>1.3</v>
       </c>
       <c r="N24">
-        <v>0.07080790960451977</v>
+        <v>0.1473922902494331</v>
       </c>
       <c r="O24">
-        <v>0.4428621908127208</v>
+        <v>0.2914798206278027</v>
       </c>
       <c r="P24">
-        <v>1.2533</v>
+        <v>1.3</v>
       </c>
       <c r="Q24">
-        <v>0.07080790960451977</v>
+        <v>0.1473922902494331</v>
       </c>
       <c r="R24">
-        <v>0.4428621908127208</v>
+        <v>0.2914798206278027</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3293,55 +3311,55 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>6.8</v>
+        <v>34.1</v>
       </c>
       <c r="V24">
-        <v>0.384180790960452</v>
+        <v>3.866213151927438</v>
       </c>
       <c r="W24">
-        <v>0.06388261851015802</v>
+        <v>0.05970548862115127</v>
       </c>
       <c r="X24">
-        <v>0.1077083405407606</v>
+        <v>0.313726937194578</v>
       </c>
       <c r="Y24">
-        <v>-0.0438257220306026</v>
+        <v>-0.2540214485734267</v>
       </c>
       <c r="Z24">
-        <v>0.05710917344806204</v>
+        <v>0.05908904390644235</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.06193807970002149</v>
+        <v>0.05225063697599236</v>
       </c>
       <c r="AC24">
-        <v>-0.06193807970002149</v>
+        <v>-0.05225063697599236</v>
       </c>
       <c r="AD24">
-        <v>50.4</v>
+        <v>219.6</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>50.4</v>
+        <v>219.6</v>
       </c>
       <c r="AG24">
-        <v>43.6</v>
+        <v>185.5</v>
       </c>
       <c r="AH24">
-        <v>0.7400881057268723</v>
+        <v>0.9613869188337274</v>
       </c>
       <c r="AI24">
-        <v>0.5526315789473685</v>
+        <v>0.7288416860272153</v>
       </c>
       <c r="AJ24">
-        <v>0.7112561174551387</v>
+        <v>0.9546109510086456</v>
       </c>
       <c r="AK24">
-        <v>0.5165876777251185</v>
+        <v>0.6942365269461078</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3367,10 +3385,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.0795</v>
+        <v>0.186</v>
       </c>
       <c r="E25">
-        <v>0.124</v>
+        <v>0.195</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3385,28 +3403,28 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>10.7</v>
+        <v>14.9</v>
       </c>
       <c r="L25">
-        <v>0.4592274678111588</v>
+        <v>0.4037940379403794</v>
       </c>
       <c r="M25">
-        <v>2.414</v>
+        <v>1.78352</v>
       </c>
       <c r="N25">
-        <v>0.06761904761904761</v>
+        <v>0.05355915915915916</v>
       </c>
       <c r="O25">
-        <v>0.225607476635514</v>
+        <v>0.1196993288590604</v>
       </c>
       <c r="P25">
-        <v>2.414</v>
+        <v>1.78352</v>
       </c>
       <c r="Q25">
-        <v>0.06761904761904761</v>
+        <v>0.05355915915915916</v>
       </c>
       <c r="R25">
-        <v>0.225607476635514</v>
+        <v>0.1196993288590604</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3415,55 +3433,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>7.96</v>
+        <v>7.48</v>
       </c>
       <c r="V25">
-        <v>0.22296918767507</v>
+        <v>0.2246246246246247</v>
       </c>
       <c r="W25">
-        <v>0.07973174366616989</v>
+        <v>0.09854497354497356</v>
       </c>
       <c r="X25">
-        <v>0.1656427857012148</v>
+        <v>0.1662335635322542</v>
       </c>
       <c r="Y25">
-        <v>-0.0859110420350449</v>
+        <v>-0.0676885899872806</v>
       </c>
       <c r="Z25">
-        <v>0.04889585602373862</v>
+        <v>0.1000433792430322</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.06222872502691684</v>
+        <v>0.05225124163573364</v>
       </c>
       <c r="AC25">
-        <v>-0.06222872502691684</v>
+        <v>-0.05225124163573364</v>
       </c>
       <c r="AD25">
-        <v>225.6</v>
+        <v>361.4</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>225.6</v>
+        <v>361.4</v>
       </c>
       <c r="AG25">
-        <v>217.64</v>
+        <v>353.92</v>
       </c>
       <c r="AH25">
-        <v>0.8633754305396096</v>
+        <v>0.915632125665062</v>
       </c>
       <c r="AI25">
-        <v>0.5987261146496816</v>
+        <v>0.6502338970852825</v>
       </c>
       <c r="AJ25">
-        <v>0.8590826557195863</v>
+        <v>0.9140023759103352</v>
       </c>
       <c r="AK25">
-        <v>0.5900661533456241</v>
+        <v>0.6454625036475051</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3480,7 +3498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aasen Sparebank (OB:AASB)</t>
+          <t>Nidaros Sparebank (OB:NISB)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3489,10 +3507,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.0549</v>
+        <v>0.081</v>
       </c>
       <c r="E26">
-        <v>0.07829999999999999</v>
+        <v>0.0934</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3507,28 +3525,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="L26">
-        <v>0.3339622641509434</v>
+        <v>0.2920353982300884</v>
       </c>
       <c r="M26">
-        <v>0.65044</v>
+        <v>0.9107799999999999</v>
       </c>
       <c r="N26">
-        <v>0.05465882352941177</v>
+        <v>0.07286239999999999</v>
       </c>
       <c r="O26">
-        <v>0.1837401129943503</v>
+        <v>0.2759939393939394</v>
       </c>
       <c r="P26">
-        <v>0.65044</v>
+        <v>0.9107799999999999</v>
       </c>
       <c r="Q26">
-        <v>0.05465882352941177</v>
+        <v>0.07286239999999999</v>
       </c>
       <c r="R26">
-        <v>0.1837401129943503</v>
+        <v>0.2759939393939394</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3537,55 +3555,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>6.58</v>
+        <v>5.98</v>
       </c>
       <c r="V26">
-        <v>0.5529411764705883</v>
+        <v>0.4784</v>
       </c>
       <c r="W26">
-        <v>0.05557299843014128</v>
+        <v>0.06573705179282868</v>
       </c>
       <c r="X26">
-        <v>0.1956510029885423</v>
+        <v>0.1262772563076868</v>
       </c>
       <c r="Y26">
-        <v>-0.140078004558401</v>
+        <v>-0.06054020451485809</v>
       </c>
       <c r="Z26">
-        <v>0.05950042099354477</v>
+        <v>0.08993235177079188</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.06229225194067885</v>
+        <v>0.05225176874598494</v>
       </c>
       <c r="AC26">
-        <v>-0.06229225194067885</v>
+        <v>-0.05225176874598494</v>
       </c>
       <c r="AD26">
-        <v>96.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>96.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AG26">
-        <v>90.02</v>
+        <v>82.11999999999999</v>
       </c>
       <c r="AH26">
-        <v>0.8903225806451612</v>
+        <v>0.8757455268389662</v>
       </c>
       <c r="AI26">
-        <v>0.638888888888889</v>
+        <v>0.6139372822299651</v>
       </c>
       <c r="AJ26">
-        <v>0.8832417582417582</v>
+        <v>0.8678926231240752</v>
       </c>
       <c r="AK26">
-        <v>0.6224588576960309</v>
+        <v>0.5971495055264688</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3602,7 +3620,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Høland og Setskog Sparebank (OB:HSPG)</t>
+          <t>Romsdal Sparebank (OB:ROMSB)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3611,10 +3629,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0415</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="E27">
-        <v>0.0226</v>
+        <v>0.204</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3629,28 +3647,28 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>4.76</v>
+        <v>6.75</v>
       </c>
       <c r="L27">
-        <v>0.34</v>
+        <v>0.3609625668449198</v>
       </c>
       <c r="M27">
-        <v>0.76</v>
+        <v>1.58956</v>
       </c>
       <c r="N27">
-        <v>0.06846846846846848</v>
+        <v>0.06881212121212121</v>
       </c>
       <c r="O27">
-        <v>0.1596638655462185</v>
+        <v>0.2354903703703704</v>
       </c>
       <c r="P27">
-        <v>0.76</v>
+        <v>1.58956</v>
       </c>
       <c r="Q27">
-        <v>0.06846846846846848</v>
+        <v>0.06881212121212121</v>
       </c>
       <c r="R27">
-        <v>0.1596638655462185</v>
+        <v>0.2354903703703704</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3659,60 +3677,301 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>33</v>
+        <v>8.25</v>
       </c>
       <c r="V27">
-        <v>2.972972972972973</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="W27">
-        <v>0.05483870967741936</v>
+        <v>0.08720930232558138</v>
       </c>
       <c r="X27">
-        <v>0.3638632689090948</v>
+        <v>0.1022700404676669</v>
       </c>
       <c r="Y27">
-        <v>-0.3090245592316754</v>
+        <v>-0.01506073814208554</v>
       </c>
       <c r="Z27">
-        <v>0.04794520547945205</v>
+        <v>0.1099482596425212</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.06242801635331277</v>
+        <v>0.05225242024645459</v>
       </c>
       <c r="AC27">
-        <v>-0.06242801635331277</v>
+        <v>-0.05225242024645459</v>
       </c>
       <c r="AD27">
-        <v>202</v>
+        <v>110</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>202</v>
+        <v>110</v>
       </c>
       <c r="AG27">
-        <v>169</v>
+        <v>101.75</v>
       </c>
       <c r="AH27">
-        <v>0.9479117785077429</v>
+        <v>0.8264462809917356</v>
       </c>
       <c r="AI27">
-        <v>0.7300325262016625</v>
+        <v>0.5612244897959183</v>
       </c>
       <c r="AJ27">
-        <v>0.9383675735702388</v>
+        <v>0.8149779735682819</v>
       </c>
       <c r="AK27">
-        <v>0.6934755847353303</v>
+        <v>0.5419440745672437</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tysnes Sparebank (OB:TYSB)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.0828</v>
+      </c>
+      <c r="E28">
+        <v>0.09630000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>3.32</v>
+      </c>
+      <c r="L28">
+        <v>0.3942992874109263</v>
+      </c>
+      <c r="M28">
+        <v>1.06972</v>
+      </c>
+      <c r="N28">
+        <v>0.04952407407407406</v>
+      </c>
+      <c r="O28">
+        <v>0.3222048192771084</v>
+      </c>
+      <c r="P28">
+        <v>1.06972</v>
+      </c>
+      <c r="Q28">
+        <v>0.04952407407407406</v>
+      </c>
+      <c r="R28">
+        <v>0.3222048192771084</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>4.2</v>
+      </c>
+      <c r="V28">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="W28">
+        <v>0.08137254901960785</v>
+      </c>
+      <c r="X28">
+        <v>0.08157976894248731</v>
+      </c>
+      <c r="Y28">
+        <v>-0.0002072199228794619</v>
+      </c>
+      <c r="Z28">
+        <v>0.09976303317535545</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.05225361202878787</v>
+      </c>
+      <c r="AC28">
+        <v>-0.05225361202878787</v>
+      </c>
+      <c r="AD28">
+        <v>60.3</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>60.3</v>
+      </c>
+      <c r="AG28">
+        <v>56.09999999999999</v>
+      </c>
+      <c r="AH28">
+        <v>0.7362637362637362</v>
+      </c>
+      <c r="AI28">
+        <v>0.5770334928229665</v>
+      </c>
+      <c r="AJ28">
+        <v>0.722007722007722</v>
+      </c>
+      <c r="AK28">
+        <v>0.559322033898305</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Instabank ASA (OB:INSTA)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0.17</v>
+      </c>
+      <c r="E29">
+        <v>0.385</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>9.48</v>
+      </c>
+      <c r="L29">
+        <v>0.3550561797752809</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>-0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>-0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.1425563909774436</v>
+      </c>
+      <c r="X29">
+        <v>0.05378290030558926</v>
+      </c>
+      <c r="Y29">
+        <v>0.08877349067185433</v>
+      </c>
+      <c r="Z29">
+        <v>0.3694990312759479</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.05226167139417419</v>
+      </c>
+      <c r="AC29">
+        <v>-0.05226167139417419</v>
+      </c>
+      <c r="AD29">
+        <v>9.42</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>9.42</v>
+      </c>
+      <c r="AG29">
+        <v>9.42</v>
+      </c>
+      <c r="AH29">
+        <v>0.1264090177133655</v>
+      </c>
+      <c r="AI29">
+        <v>0.09800249687890136</v>
+      </c>
+      <c r="AJ29">
+        <v>0.1264090177133655</v>
+      </c>
+      <c r="AK29">
+        <v>0.09800249687890136</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
         <v>0</v>
       </c>
     </row>
